--- a/research/traditional_assets/database/data/israel/israel_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_paper_forest_products.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08880490204333993</v>
+        <v>0.08863530076864028</v>
       </c>
       <c r="C2">
-        <v>156.80881724047</v>
+        <v>155.7752800701581</v>
       </c>
       <c r="D2">
-        <v>153.92881724047</v>
+        <v>154.5382800701581</v>
       </c>
       <c r="E2">
-        <v>-90.7</v>
+        <v>-89.057</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.643</v>
       </c>
       <c r="G2">
         <v>2.88</v>
@@ -1451,28 +1451,28 @@
         <v>17.925</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.08264290000000001</v>
       </c>
       <c r="N2">
-        <v>17.925</v>
+        <v>17.8423571</v>
       </c>
       <c r="O2">
-        <v>4.12275</v>
+        <v>4.103742133000001</v>
       </c>
       <c r="P2">
-        <v>13.80225</v>
+        <v>13.738614967</v>
       </c>
       <c r="Q2">
-        <v>24.00225</v>
+        <v>23.938614967</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08880490204333993</v>
+        <v>0.08913938461478815</v>
       </c>
       <c r="T2">
-        <v>0.6652721574126822</v>
+        <v>0.6704464964147809</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>216.8970353170085</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08863530076864028</v>
+        <v>0.08846569949394058</v>
       </c>
       <c r="C3">
-        <v>155.7752800701581</v>
+        <v>154.7465882755942</v>
       </c>
       <c r="D3">
-        <v>154.5382800701581</v>
+        <v>155.1525882755942</v>
       </c>
       <c r="E3">
-        <v>-89.057</v>
+        <v>-87.414</v>
       </c>
       <c r="F3">
-        <v>1.643</v>
+        <v>3.286</v>
       </c>
       <c r="G3">
         <v>2.88</v>
@@ -1533,28 +1533,28 @@
         <v>17.925</v>
       </c>
       <c r="M3">
-        <v>0.08264290000000001</v>
+        <v>0.1652858</v>
       </c>
       <c r="N3">
-        <v>17.8423571</v>
+        <v>17.7597142</v>
       </c>
       <c r="O3">
-        <v>4.103742133000001</v>
+        <v>4.084734266000001</v>
       </c>
       <c r="P3">
-        <v>13.738614967</v>
+        <v>13.674979934</v>
       </c>
       <c r="Q3">
-        <v>23.938614967</v>
+        <v>23.874979934</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08913938461478815</v>
+        <v>0.08948069336116385</v>
       </c>
       <c r="T3">
-        <v>0.6704464964147809</v>
+        <v>0.6757264341720244</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>216.8970353170085</v>
+        <v>108.4485176585042</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08846569949394058</v>
+        <v>0.08829609821924089</v>
       </c>
       <c r="C4">
-        <v>154.7465882755942</v>
+        <v>153.7227998702384</v>
       </c>
       <c r="D4">
-        <v>155.1525882755942</v>
+        <v>155.7717998702385</v>
       </c>
       <c r="E4">
-        <v>-87.414</v>
+        <v>-85.771</v>
       </c>
       <c r="F4">
-        <v>3.286</v>
+        <v>4.929</v>
       </c>
       <c r="G4">
         <v>2.88</v>
@@ -1615,28 +1615,28 @@
         <v>17.925</v>
       </c>
       <c r="M4">
-        <v>0.1652858</v>
+        <v>0.2479287</v>
       </c>
       <c r="N4">
-        <v>17.7597142</v>
+        <v>17.6770713</v>
       </c>
       <c r="O4">
-        <v>4.084734266000001</v>
+        <v>4.065726399000001</v>
       </c>
       <c r="P4">
-        <v>13.674979934</v>
+        <v>13.611344901</v>
       </c>
       <c r="Q4">
-        <v>23.874979934</v>
+        <v>23.811344901</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08948069336116385</v>
+        <v>0.08982903940127927</v>
       </c>
       <c r="T4">
-        <v>0.6757264341720244</v>
+        <v>0.6811152366252935</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>108.4485176585042</v>
+        <v>72.29901177233617</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08829609821924089</v>
+        <v>0.08812649694454119</v>
       </c>
       <c r="C5">
-        <v>153.7227998702384</v>
+        <v>152.7039737973857</v>
       </c>
       <c r="D5">
-        <v>155.7717998702385</v>
+        <v>156.3959737973857</v>
       </c>
       <c r="E5">
-        <v>-85.771</v>
+        <v>-84.128</v>
       </c>
       <c r="F5">
-        <v>4.929</v>
+        <v>6.572000000000001</v>
       </c>
       <c r="G5">
         <v>2.88</v>
@@ -1697,28 +1697,28 @@
         <v>17.925</v>
       </c>
       <c r="M5">
-        <v>0.2479287</v>
+        <v>0.3305716</v>
       </c>
       <c r="N5">
-        <v>17.6770713</v>
+        <v>17.5944284</v>
       </c>
       <c r="O5">
-        <v>4.065726399000001</v>
+        <v>4.046718532000001</v>
       </c>
       <c r="P5">
-        <v>13.611344901</v>
+        <v>13.547709868</v>
       </c>
       <c r="Q5">
-        <v>23.811344901</v>
+        <v>23.747709868</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08982903940127927</v>
+        <v>0.09018464265056375</v>
       </c>
       <c r="T5">
-        <v>0.6811152366252935</v>
+        <v>0.686616305796339</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>72.29901177233617</v>
+        <v>54.22425882925212</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08812649694454119</v>
+        <v>0.08795689566984154</v>
       </c>
       <c r="C6">
-        <v>152.7039737973857</v>
+        <v>151.6901699488686</v>
       </c>
       <c r="D6">
-        <v>156.3959737973857</v>
+        <v>157.0251699488686</v>
       </c>
       <c r="E6">
-        <v>-84.128</v>
+        <v>-82.485</v>
       </c>
       <c r="F6">
-        <v>6.572000000000001</v>
+        <v>8.215000000000002</v>
       </c>
       <c r="G6">
         <v>2.88</v>
@@ -1779,28 +1779,28 @@
         <v>17.925</v>
       </c>
       <c r="M6">
-        <v>0.3305716</v>
+        <v>0.4132145</v>
       </c>
       <c r="N6">
-        <v>17.5944284</v>
+        <v>17.5117855</v>
       </c>
       <c r="O6">
-        <v>4.046718532000001</v>
+        <v>4.027710665000001</v>
       </c>
       <c r="P6">
-        <v>13.547709868</v>
+        <v>13.484074835</v>
       </c>
       <c r="Q6">
-        <v>23.747709868</v>
+        <v>23.684074835</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09018464265056375</v>
+        <v>0.09054773228404372</v>
       </c>
       <c r="T6">
-        <v>0.686616305796339</v>
+        <v>0.6922331869499331</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>54.22425882925212</v>
+        <v>43.37940706340169</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08795689566984154</v>
+        <v>0.08778729439514184</v>
       </c>
       <c r="C7">
-        <v>151.6901699488686</v>
+        <v>150.6814491842162</v>
       </c>
       <c r="D7">
-        <v>157.0251699488686</v>
+        <v>157.6594491842162</v>
       </c>
       <c r="E7">
-        <v>-82.485</v>
+        <v>-80.842</v>
       </c>
       <c r="F7">
-        <v>8.215000000000002</v>
+        <v>9.858000000000002</v>
       </c>
       <c r="G7">
         <v>2.88</v>
@@ -1861,28 +1861,28 @@
         <v>17.925</v>
       </c>
       <c r="M7">
-        <v>0.4132145</v>
+        <v>0.4958574000000001</v>
       </c>
       <c r="N7">
-        <v>17.5117855</v>
+        <v>17.4291426</v>
       </c>
       <c r="O7">
-        <v>4.027710665000001</v>
+        <v>4.008702798000001</v>
       </c>
       <c r="P7">
-        <v>13.484074835</v>
+        <v>13.420439802</v>
       </c>
       <c r="Q7">
-        <v>23.684074835</v>
+        <v>23.620439802</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09054773228404372</v>
+        <v>0.09091854722887431</v>
       </c>
       <c r="T7">
-        <v>0.6922331869499331</v>
+        <v>0.6979695762131779</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>43.37940706340169</v>
+        <v>36.14950588616808</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08778729439514184</v>
+        <v>0.08761769312044215</v>
       </c>
       <c r="C8">
-        <v>150.6814491842162</v>
+        <v>149.6778733502762</v>
       </c>
       <c r="D8">
-        <v>157.6594491842162</v>
+        <v>158.2988733502762</v>
       </c>
       <c r="E8">
-        <v>-80.842</v>
+        <v>-79.199</v>
       </c>
       <c r="F8">
-        <v>9.858000000000001</v>
+        <v>11.501</v>
       </c>
       <c r="G8">
         <v>2.88</v>
@@ -1943,28 +1943,28 @@
         <v>17.925</v>
       </c>
       <c r="M8">
-        <v>0.4958574</v>
+        <v>0.5785003</v>
       </c>
       <c r="N8">
-        <v>17.4291426</v>
+        <v>17.3464997</v>
       </c>
       <c r="O8">
-        <v>4.008702798000001</v>
+        <v>3.989694931000001</v>
       </c>
       <c r="P8">
-        <v>13.420439802</v>
+        <v>13.356804769</v>
       </c>
       <c r="Q8">
-        <v>23.620439802</v>
+        <v>23.556804769</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0909185472288743</v>
+        <v>0.09129733668864748</v>
       </c>
       <c r="T8">
-        <v>0.6979695762131778</v>
+        <v>0.7038293286863849</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.14950588616809</v>
+        <v>30.98529075957265</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08761769312044215</v>
+        <v>0.0874480918457425</v>
       </c>
       <c r="C9">
-        <v>149.6778733502762</v>
+        <v>148.6795053013189</v>
       </c>
       <c r="D9">
-        <v>158.2988733502762</v>
+        <v>158.9435053013189</v>
       </c>
       <c r="E9">
-        <v>-79.199</v>
+        <v>-77.556</v>
       </c>
       <c r="F9">
-        <v>11.501</v>
+        <v>13.144</v>
       </c>
       <c r="G9">
         <v>2.88</v>
@@ -2025,28 +2025,28 @@
         <v>17.925</v>
       </c>
       <c r="M9">
-        <v>0.5785003000000001</v>
+        <v>0.6611432</v>
       </c>
       <c r="N9">
-        <v>17.3464997</v>
+        <v>17.2638568</v>
       </c>
       <c r="O9">
-        <v>3.989694931</v>
+        <v>3.970687064</v>
       </c>
       <c r="P9">
-        <v>13.356804769</v>
+        <v>13.293169736</v>
       </c>
       <c r="Q9">
-        <v>23.556804769</v>
+        <v>23.493169736</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09129733668864748</v>
+        <v>0.09168436070189401</v>
       </c>
       <c r="T9">
-        <v>0.7038293286863849</v>
+        <v>0.7098164670829226</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>30.98529075957264</v>
+        <v>27.11212941462606</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0874480918457425</v>
+        <v>0.08727849057104281</v>
       </c>
       <c r="C10">
-        <v>148.6795053013189</v>
+        <v>147.6864089196333</v>
       </c>
       <c r="D10">
-        <v>158.9435053013189</v>
+        <v>159.5934089196333</v>
       </c>
       <c r="E10">
-        <v>-77.556</v>
+        <v>-75.913</v>
       </c>
       <c r="F10">
-        <v>13.144</v>
+        <v>14.787</v>
       </c>
       <c r="G10">
         <v>2.88</v>
@@ -2107,28 +2107,28 @@
         <v>17.925</v>
       </c>
       <c r="M10">
-        <v>0.6611432</v>
+        <v>0.7437861</v>
       </c>
       <c r="N10">
-        <v>17.2638568</v>
+        <v>17.1812139</v>
       </c>
       <c r="O10">
-        <v>3.970687064</v>
+        <v>3.951679197</v>
       </c>
       <c r="P10">
-        <v>13.293169736</v>
+        <v>13.229534703</v>
       </c>
       <c r="Q10">
-        <v>23.493169736</v>
+        <v>23.429534703</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09168436070189401</v>
+        <v>0.09207989073740967</v>
       </c>
       <c r="T10">
-        <v>0.7098164670829226</v>
+        <v>0.7159351909387249</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.11212941462606</v>
+        <v>24.09967059077872</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08727849057104281</v>
+        <v>0.08710888929634313</v>
       </c>
       <c r="C11">
-        <v>147.6864089196333</v>
+        <v>146.6986491366302</v>
       </c>
       <c r="D11">
-        <v>159.5934089196333</v>
+        <v>160.2486491366302</v>
       </c>
       <c r="E11">
-        <v>-75.913</v>
+        <v>-74.27000000000001</v>
       </c>
       <c r="F11">
-        <v>14.787</v>
+        <v>16.43</v>
       </c>
       <c r="G11">
         <v>2.88</v>
@@ -2189,28 +2189,28 @@
         <v>17.925</v>
       </c>
       <c r="M11">
-        <v>0.7437861</v>
+        <v>0.826429</v>
       </c>
       <c r="N11">
-        <v>17.1812139</v>
+        <v>17.098571</v>
       </c>
       <c r="O11">
-        <v>3.951679197</v>
+        <v>3.93267133</v>
       </c>
       <c r="P11">
-        <v>13.229534703</v>
+        <v>13.16589967</v>
       </c>
       <c r="Q11">
-        <v>23.429534703</v>
+        <v>23.36589967</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09207989073740967</v>
+        <v>0.09248421032927014</v>
       </c>
       <c r="T11">
-        <v>0.7159351909387249</v>
+        <v>0.7221898864357673</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.09967059077872</v>
+        <v>21.68970353170085</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08710888929634313</v>
+        <v>0.08693928802164344</v>
       </c>
       <c r="C12">
-        <v>146.6986491366302</v>
+        <v>145.7162919544684</v>
       </c>
       <c r="D12">
-        <v>160.2486491366302</v>
+        <v>160.9092919544684</v>
       </c>
       <c r="E12">
-        <v>-74.27</v>
+        <v>-72.62700000000001</v>
       </c>
       <c r="F12">
-        <v>16.43</v>
+        <v>18.073</v>
       </c>
       <c r="G12">
         <v>2.88</v>
@@ -2271,28 +2271,28 @@
         <v>17.925</v>
       </c>
       <c r="M12">
-        <v>0.8264290000000001</v>
+        <v>0.9090718999999999</v>
       </c>
       <c r="N12">
-        <v>17.098571</v>
+        <v>17.0159281</v>
       </c>
       <c r="O12">
-        <v>3.93267133</v>
+        <v>3.913663463</v>
       </c>
       <c r="P12">
-        <v>13.16589967</v>
+        <v>13.102264637</v>
       </c>
       <c r="Q12">
-        <v>23.36589967</v>
+        <v>23.302264637</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09248421032927014</v>
+        <v>0.09289761575465555</v>
       </c>
       <c r="T12">
-        <v>0.7221898864357673</v>
+        <v>0.7285851368877994</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.68970353170085</v>
+        <v>19.71791230154623</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08693928802164344</v>
+        <v>0.08676968674694374</v>
       </c>
       <c r="C13">
-        <v>145.7162919544684</v>
+        <v>144.7394044682171</v>
       </c>
       <c r="D13">
-        <v>160.9092919544684</v>
+        <v>161.5754044682171</v>
       </c>
       <c r="E13">
-        <v>-72.62700000000001</v>
+        <v>-70.98400000000001</v>
       </c>
       <c r="F13">
-        <v>18.073</v>
+        <v>19.716</v>
       </c>
       <c r="G13">
         <v>2.88</v>
@@ -2353,28 +2353,28 @@
         <v>17.925</v>
       </c>
       <c r="M13">
-        <v>0.9090718999999999</v>
+        <v>0.9917148</v>
       </c>
       <c r="N13">
-        <v>17.0159281</v>
+        <v>16.9332852</v>
       </c>
       <c r="O13">
-        <v>3.913663463</v>
+        <v>3.894655596</v>
       </c>
       <c r="P13">
-        <v>13.102264637</v>
+        <v>13.038629604</v>
       </c>
       <c r="Q13">
-        <v>23.302264637</v>
+        <v>23.238629604</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09289761575465555</v>
+        <v>0.09332041675789063</v>
       </c>
       <c r="T13">
-        <v>0.7285851368877994</v>
+        <v>0.7351257339410138</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.71791230154623</v>
+        <v>18.07475294308404</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08676968674694374</v>
+        <v>0.08660008547224407</v>
       </c>
       <c r="C14">
-        <v>144.7394044682171</v>
+        <v>143.7680548885714</v>
       </c>
       <c r="D14">
-        <v>161.5754044682171</v>
+        <v>162.2470548885715</v>
       </c>
       <c r="E14">
-        <v>-70.98400000000001</v>
+        <v>-69.34100000000001</v>
       </c>
       <c r="F14">
-        <v>19.716</v>
+        <v>21.359</v>
       </c>
       <c r="G14">
         <v>2.88</v>
@@ -2435,28 +2435,28 @@
         <v>17.925</v>
       </c>
       <c r="M14">
-        <v>0.9917148</v>
+        <v>1.0743577</v>
       </c>
       <c r="N14">
-        <v>16.9332852</v>
+        <v>16.8506423</v>
       </c>
       <c r="O14">
-        <v>3.894655596</v>
+        <v>3.875647729</v>
       </c>
       <c r="P14">
-        <v>13.038629604</v>
+        <v>12.974994571</v>
       </c>
       <c r="Q14">
-        <v>23.238629604</v>
+        <v>23.174994571</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09332041675789063</v>
+        <v>0.09375293732441847</v>
       </c>
       <c r="T14">
-        <v>0.7351257339410138</v>
+        <v>0.7418166895471758</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.07475294308404</v>
+        <v>16.68438733207758</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08660008547224407</v>
+        <v>0.0864304841975444</v>
       </c>
       <c r="C15">
-        <v>143.7680548885714</v>
+        <v>142.8023125651371</v>
       </c>
       <c r="D15">
-        <v>162.2470548885715</v>
+        <v>162.9243125651371</v>
       </c>
       <c r="E15">
-        <v>-69.34100000000001</v>
+        <v>-67.69800000000001</v>
       </c>
       <c r="F15">
-        <v>21.359</v>
+        <v>23.002</v>
       </c>
       <c r="G15">
         <v>2.88</v>
@@ -2517,28 +2517,28 @@
         <v>17.925</v>
       </c>
       <c r="M15">
-        <v>1.0743577</v>
+        <v>1.1570006</v>
       </c>
       <c r="N15">
-        <v>16.8506423</v>
+        <v>16.7679994</v>
       </c>
       <c r="O15">
-        <v>3.875647729</v>
+        <v>3.856639862</v>
       </c>
       <c r="P15">
-        <v>12.974994571</v>
+        <v>12.911359538</v>
       </c>
       <c r="Q15">
-        <v>23.174994571</v>
+        <v>23.111359538</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09375293732441847</v>
+        <v>0.09419551650877256</v>
       </c>
       <c r="T15">
-        <v>0.7418166895471758</v>
+        <v>0.7486632487720859</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.68438733207758</v>
+        <v>15.49264537978632</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0864304841975444</v>
+        <v>0.08626088292284471</v>
       </c>
       <c r="C16">
-        <v>142.8023125651371</v>
+        <v>141.8422480103005</v>
       </c>
       <c r="D16">
-        <v>162.9243125651371</v>
+        <v>163.6072480103005</v>
       </c>
       <c r="E16">
-        <v>-67.69800000000001</v>
+        <v>-66.05499999999999</v>
       </c>
       <c r="F16">
-        <v>23.002</v>
+        <v>24.64500000000001</v>
       </c>
       <c r="G16">
         <v>2.88</v>
@@ -2599,28 +2599,28 @@
         <v>17.925</v>
       </c>
       <c r="M16">
-        <v>1.1570006</v>
+        <v>1.2396435</v>
       </c>
       <c r="N16">
-        <v>16.7679994</v>
+        <v>16.6853565</v>
       </c>
       <c r="O16">
-        <v>3.856639862</v>
+        <v>3.837631995</v>
       </c>
       <c r="P16">
-        <v>12.911359538</v>
+        <v>12.847724505</v>
       </c>
       <c r="Q16">
-        <v>23.111359538</v>
+        <v>23.047724505</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09419551650877256</v>
+        <v>0.09464850932099378</v>
       </c>
       <c r="T16">
-        <v>0.7486632487720859</v>
+        <v>0.7556709035081702</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.49264537978632</v>
+        <v>14.45980235446723</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08626088292284471</v>
+        <v>0.08609128164814502</v>
       </c>
       <c r="C17">
-        <v>141.8422480103005</v>
+        <v>140.8879329237012</v>
       </c>
       <c r="D17">
-        <v>163.6072480103005</v>
+        <v>164.2959329237013</v>
       </c>
       <c r="E17">
-        <v>-66.05500000000001</v>
+        <v>-64.41200000000001</v>
       </c>
       <c r="F17">
-        <v>24.645</v>
+        <v>26.288</v>
       </c>
       <c r="G17">
         <v>2.88</v>
@@ -2681,28 +2681,28 @@
         <v>17.925</v>
       </c>
       <c r="M17">
-        <v>1.2396435</v>
+        <v>1.3222864</v>
       </c>
       <c r="N17">
-        <v>16.6853565</v>
+        <v>16.6027136</v>
       </c>
       <c r="O17">
-        <v>3.837631995</v>
+        <v>3.818624128000001</v>
       </c>
       <c r="P17">
-        <v>12.847724505</v>
+        <v>12.784089472</v>
       </c>
       <c r="Q17">
-        <v>23.047724505</v>
+        <v>22.984089472</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09464850932099378</v>
+        <v>0.09511228767636312</v>
       </c>
       <c r="T17">
-        <v>0.7556709035081702</v>
+        <v>0.7628454071665423</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.45980235446723</v>
+        <v>13.55606470731303</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08609128164814502</v>
+        <v>0.08611803037344534</v>
       </c>
       <c r="C18">
-        <v>140.8879329237012</v>
+        <v>139.1359318952028</v>
       </c>
       <c r="D18">
-        <v>164.2959329237013</v>
+        <v>164.1869318952028</v>
       </c>
       <c r="E18">
-        <v>-64.41200000000001</v>
+        <v>-62.769</v>
       </c>
       <c r="F18">
-        <v>26.288</v>
+        <v>27.931</v>
       </c>
       <c r="G18">
         <v>2.88</v>
@@ -2763,45 +2763,45 @@
         <v>17.925</v>
       </c>
       <c r="M18">
-        <v>1.3222864</v>
+        <v>1.4468258</v>
       </c>
       <c r="N18">
-        <v>16.6027136</v>
+        <v>16.4781742</v>
       </c>
       <c r="O18">
-        <v>3.818624128000001</v>
+        <v>3.789980066</v>
       </c>
       <c r="P18">
-        <v>12.784089472</v>
+        <v>12.688194134</v>
       </c>
       <c r="Q18">
-        <v>22.984089472</v>
+        <v>22.888194134</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09511228767636312</v>
+        <v>0.09558724141378958</v>
       </c>
       <c r="T18">
-        <v>0.7628454071665423</v>
+        <v>0.7701927904311401</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.23</v>
       </c>
       <c r="W18">
-        <v>0.038731</v>
+        <v>0.039886</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.55606470731303</v>
+        <v>12.38919018447141</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08611803037344534</v>
+        <v>0.08595997909874566</v>
       </c>
       <c r="C19">
-        <v>139.1359318952028</v>
+        <v>138.1390964216151</v>
       </c>
       <c r="D19">
-        <v>164.1869318952028</v>
+        <v>164.8330964216151</v>
       </c>
       <c r="E19">
-        <v>-62.769</v>
+        <v>-61.126</v>
       </c>
       <c r="F19">
-        <v>27.931</v>
+        <v>29.57400000000001</v>
       </c>
       <c r="G19">
         <v>2.88</v>
@@ -2845,28 +2845,28 @@
         <v>17.925</v>
       </c>
       <c r="M19">
-        <v>1.4468258</v>
+        <v>1.5319332</v>
       </c>
       <c r="N19">
-        <v>16.4781742</v>
+        <v>16.3930668</v>
       </c>
       <c r="O19">
-        <v>3.789980066</v>
+        <v>3.770405364</v>
       </c>
       <c r="P19">
-        <v>12.688194134</v>
+        <v>12.622661436</v>
       </c>
       <c r="Q19">
-        <v>22.888194134</v>
+        <v>22.822661436</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09558724141378958</v>
+        <v>0.09607377938871423</v>
       </c>
       <c r="T19">
-        <v>0.7701927904311401</v>
+        <v>0.7777193781656062</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.38919018447141</v>
+        <v>11.70090184088967</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08595997909874567</v>
+        <v>0.085801927824046</v>
       </c>
       <c r="C20">
-        <v>138.139096421615</v>
+        <v>137.1473670582884</v>
       </c>
       <c r="D20">
-        <v>164.833096421615</v>
+        <v>165.4843670582885</v>
       </c>
       <c r="E20">
-        <v>-61.126</v>
+        <v>-59.483</v>
       </c>
       <c r="F20">
-        <v>29.574</v>
+        <v>31.217</v>
       </c>
       <c r="G20">
         <v>2.88</v>
@@ -2927,28 +2927,28 @@
         <v>17.925</v>
       </c>
       <c r="M20">
-        <v>1.5319332</v>
+        <v>1.6170406</v>
       </c>
       <c r="N20">
-        <v>16.3930668</v>
+        <v>16.3079594</v>
       </c>
       <c r="O20">
-        <v>3.770405364</v>
+        <v>3.750830662000001</v>
       </c>
       <c r="P20">
-        <v>12.622661436</v>
+        <v>12.557128738</v>
       </c>
       <c r="Q20">
-        <v>22.822661436</v>
+        <v>22.757128738</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09607377938871423</v>
+        <v>0.09657233064697035</v>
       </c>
       <c r="T20">
-        <v>0.7777193781656062</v>
+        <v>0.7854318075725284</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.70090184088967</v>
+        <v>11.08506490189547</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.085801927824046</v>
+        <v>0.0856438765493463</v>
       </c>
       <c r="C21">
-        <v>137.1473670582884</v>
+        <v>136.1608045694338</v>
       </c>
       <c r="D21">
-        <v>165.4843670582885</v>
+        <v>166.1408045694338</v>
       </c>
       <c r="E21">
-        <v>-59.483</v>
+        <v>-57.84</v>
       </c>
       <c r="F21">
-        <v>31.217</v>
+        <v>32.86000000000001</v>
       </c>
       <c r="G21">
         <v>2.88</v>
@@ -3009,28 +3009,28 @@
         <v>17.925</v>
       </c>
       <c r="M21">
-        <v>1.6170406</v>
+        <v>1.702148</v>
       </c>
       <c r="N21">
-        <v>16.3079594</v>
+        <v>16.222852</v>
       </c>
       <c r="O21">
-        <v>3.750830662000001</v>
+        <v>3.73125596</v>
       </c>
       <c r="P21">
-        <v>12.557128738</v>
+        <v>12.49159604</v>
       </c>
       <c r="Q21">
-        <v>22.757128738</v>
+        <v>22.69159604</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09657233064697035</v>
+        <v>0.09708334568668286</v>
       </c>
       <c r="T21">
-        <v>0.7854318075725284</v>
+        <v>0.7933370477146234</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.08506490189547</v>
+        <v>10.5308116568007</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0856438765493463</v>
+        <v>0.08548582527464663</v>
       </c>
       <c r="C22">
-        <v>136.1608045694338</v>
+        <v>135.1794706872505</v>
       </c>
       <c r="D22">
-        <v>166.1408045694338</v>
+        <v>166.8024706872505</v>
       </c>
       <c r="E22">
-        <v>-57.84</v>
+        <v>-56.197</v>
       </c>
       <c r="F22">
-        <v>32.86000000000001</v>
+        <v>34.50300000000001</v>
       </c>
       <c r="G22">
         <v>2.88</v>
@@ -3091,28 +3091,28 @@
         <v>17.925</v>
       </c>
       <c r="M22">
-        <v>1.702148</v>
+        <v>1.7872554</v>
       </c>
       <c r="N22">
-        <v>16.222852</v>
+        <v>16.1377446</v>
       </c>
       <c r="O22">
-        <v>3.73125596</v>
+        <v>3.711681258</v>
       </c>
       <c r="P22">
-        <v>12.49159604</v>
+        <v>12.426063342</v>
       </c>
       <c r="Q22">
-        <v>22.69159604</v>
+        <v>22.626063342</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09708334568668286</v>
+        <v>0.09760729781600838</v>
       </c>
       <c r="T22">
-        <v>0.7933370477146234</v>
+        <v>0.8014424205185439</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.5308116568007</v>
+        <v>10.02934443504829</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08548582527464663</v>
+        <v>0.08561575399994693</v>
       </c>
       <c r="C23">
-        <v>135.1794706872505</v>
+        <v>132.9921526669672</v>
       </c>
       <c r="D23">
-        <v>166.8024706872505</v>
+        <v>166.2581526669672</v>
       </c>
       <c r="E23">
-        <v>-56.197</v>
+        <v>-54.554</v>
       </c>
       <c r="F23">
-        <v>34.503</v>
+        <v>36.146</v>
       </c>
       <c r="G23">
         <v>2.88</v>
@@ -3173,45 +3173,45 @@
         <v>17.925</v>
       </c>
       <c r="M23">
-        <v>1.7872554</v>
+        <v>1.933811</v>
       </c>
       <c r="N23">
-        <v>16.1377446</v>
+        <v>15.991189</v>
       </c>
       <c r="O23">
-        <v>3.711681258</v>
+        <v>3.67797347</v>
       </c>
       <c r="P23">
-        <v>12.426063342</v>
+        <v>12.31321553</v>
       </c>
       <c r="Q23">
-        <v>22.626063342</v>
+        <v>22.51321553</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09760729781600838</v>
+        <v>0.09814468461531659</v>
       </c>
       <c r="T23">
-        <v>0.8014424205185439</v>
+        <v>0.8097556233943596</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.23</v>
       </c>
       <c r="W23">
-        <v>0.039886</v>
+        <v>0.041195</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>10.02934443504829</v>
+        <v>9.269261577268926</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08561575399994693</v>
+        <v>0.08547079272524727</v>
       </c>
       <c r="C24">
-        <v>132.9921526669672</v>
+        <v>131.956677550746</v>
       </c>
       <c r="D24">
-        <v>166.2581526669672</v>
+        <v>166.865677550746</v>
       </c>
       <c r="E24">
-        <v>-54.554</v>
+        <v>-52.911</v>
       </c>
       <c r="F24">
-        <v>36.146</v>
+        <v>37.789</v>
       </c>
       <c r="G24">
         <v>2.88</v>
@@ -3255,28 +3255,28 @@
         <v>17.925</v>
       </c>
       <c r="M24">
-        <v>1.933811</v>
+        <v>2.0217115</v>
       </c>
       <c r="N24">
-        <v>15.991189</v>
+        <v>15.9032885</v>
       </c>
       <c r="O24">
-        <v>3.67797347</v>
+        <v>3.657756355</v>
       </c>
       <c r="P24">
-        <v>12.31321553</v>
+        <v>12.245532145</v>
       </c>
       <c r="Q24">
-        <v>22.51321553</v>
+        <v>22.445532145</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09814468461531659</v>
+        <v>0.09869602951330812</v>
       </c>
       <c r="T24">
-        <v>0.8097556233943596</v>
+        <v>0.8182847536175991</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.269261577268926</v>
+        <v>8.86625020434419</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08547079272524727</v>
+        <v>0.08532583145054758</v>
       </c>
       <c r="C25">
-        <v>131.956677550746</v>
+        <v>130.9256586383961</v>
       </c>
       <c r="D25">
-        <v>166.865677550746</v>
+        <v>167.4776586383962</v>
       </c>
       <c r="E25">
-        <v>-52.911</v>
+        <v>-51.26799999999999</v>
       </c>
       <c r="F25">
-        <v>37.789</v>
+        <v>39.43200000000001</v>
       </c>
       <c r="G25">
         <v>2.88</v>
@@ -3337,28 +3337,28 @@
         <v>17.925</v>
       </c>
       <c r="M25">
-        <v>2.0217115</v>
+        <v>2.109612</v>
       </c>
       <c r="N25">
-        <v>15.9032885</v>
+        <v>15.815388</v>
       </c>
       <c r="O25">
-        <v>3.657756355</v>
+        <v>3.63753924</v>
       </c>
       <c r="P25">
-        <v>12.245532145</v>
+        <v>12.17784876</v>
       </c>
       <c r="Q25">
-        <v>22.445532145</v>
+        <v>22.37784876</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09869602951330812</v>
+        <v>0.0992618834875626</v>
       </c>
       <c r="T25">
-        <v>0.8182847536175991</v>
+        <v>0.8270383346361869</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.86625020434419</v>
+        <v>8.496823112496514</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08532583145054758</v>
+        <v>0.08518087017584788</v>
       </c>
       <c r="C26">
-        <v>130.9256586383962</v>
+        <v>129.899145139876</v>
       </c>
       <c r="D26">
-        <v>167.4776586383962</v>
+        <v>168.094145139876</v>
       </c>
       <c r="E26">
-        <v>-51.268</v>
+        <v>-49.625</v>
       </c>
       <c r="F26">
-        <v>39.432</v>
+        <v>41.075</v>
       </c>
       <c r="G26">
         <v>2.88</v>
@@ -3419,28 +3419,28 @@
         <v>17.925</v>
       </c>
       <c r="M26">
-        <v>2.109612</v>
+        <v>2.1975125</v>
       </c>
       <c r="N26">
-        <v>15.815388</v>
+        <v>15.7274875</v>
       </c>
       <c r="O26">
-        <v>3.63753924</v>
+        <v>3.617322125</v>
       </c>
       <c r="P26">
-        <v>12.17784876</v>
+        <v>12.110165375</v>
       </c>
       <c r="Q26">
-        <v>22.37784876</v>
+        <v>22.310165375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0992618834875626</v>
+        <v>0.09984282690113053</v>
       </c>
       <c r="T26">
-        <v>0.8270383346361869</v>
+        <v>0.8360253444819372</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.496823112496514</v>
+        <v>8.156950187996655</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08518087017584788</v>
+        <v>0.08503590890114822</v>
       </c>
       <c r="C27">
-        <v>129.899145139876</v>
+        <v>128.8771869923897</v>
       </c>
       <c r="D27">
-        <v>168.094145139876</v>
+        <v>168.7151869923897</v>
       </c>
       <c r="E27">
-        <v>-49.625</v>
+        <v>-47.982</v>
       </c>
       <c r="F27">
-        <v>41.075</v>
+        <v>42.718</v>
       </c>
       <c r="G27">
         <v>2.88</v>
@@ -3501,28 +3501,28 @@
         <v>17.925</v>
       </c>
       <c r="M27">
-        <v>2.1975125</v>
+        <v>2.285413</v>
       </c>
       <c r="N27">
-        <v>15.7274875</v>
+        <v>15.639587</v>
       </c>
       <c r="O27">
-        <v>3.617322125</v>
+        <v>3.59710501</v>
       </c>
       <c r="P27">
-        <v>12.110165375</v>
+        <v>12.04248199</v>
       </c>
       <c r="Q27">
-        <v>22.310165375</v>
+        <v>22.24248199</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09984282690113053</v>
+        <v>0.1004394714880381</v>
       </c>
       <c r="T27">
-        <v>0.8360253444819372</v>
+        <v>0.8452552464856808</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.156950187996655</v>
+        <v>7.843221334612168</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08503590890114822</v>
+        <v>0.08505726762644852</v>
       </c>
       <c r="C28">
-        <v>128.8771869923897</v>
+        <v>127.1423940187358</v>
       </c>
       <c r="D28">
-        <v>168.7151869923897</v>
+        <v>168.6233940187358</v>
       </c>
       <c r="E28">
-        <v>-47.982</v>
+        <v>-46.339</v>
       </c>
       <c r="F28">
-        <v>42.718</v>
+        <v>44.361</v>
       </c>
       <c r="G28">
         <v>2.88</v>
@@ -3583,45 +3583,45 @@
         <v>17.925</v>
       </c>
       <c r="M28">
-        <v>2.285413</v>
+        <v>2.4088023</v>
       </c>
       <c r="N28">
-        <v>15.639587</v>
+        <v>15.5161977</v>
       </c>
       <c r="O28">
-        <v>3.59710501</v>
+        <v>3.568725471</v>
       </c>
       <c r="P28">
-        <v>12.04248199</v>
+        <v>11.947472229</v>
       </c>
       <c r="Q28">
-        <v>22.24248199</v>
+        <v>22.147472229</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1004394714880381</v>
+        <v>0.1010524625019843</v>
       </c>
       <c r="T28">
-        <v>0.8452552464856808</v>
+        <v>0.8547380225169241</v>
       </c>
       <c r="U28">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V28">
         <v>0.23</v>
       </c>
       <c r="W28">
-        <v>0.041195</v>
+        <v>0.041811</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y28">
-        <v>7.843221334612168</v>
+        <v>7.441457524347266</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08505726762644852</v>
+        <v>0.08491846635174885</v>
       </c>
       <c r="C29">
-        <v>127.1423940187358</v>
+        <v>126.0977084266558</v>
       </c>
       <c r="D29">
-        <v>168.6233940187358</v>
+        <v>169.2217084266558</v>
       </c>
       <c r="E29">
-        <v>-46.339</v>
+        <v>-44.696</v>
       </c>
       <c r="F29">
-        <v>44.361</v>
+        <v>46.004</v>
       </c>
       <c r="G29">
         <v>2.88</v>
@@ -3665,28 +3665,28 @@
         <v>17.925</v>
       </c>
       <c r="M29">
-        <v>2.4088023</v>
+        <v>2.4980172</v>
       </c>
       <c r="N29">
-        <v>15.5161977</v>
+        <v>15.4269828</v>
       </c>
       <c r="O29">
-        <v>3.568725471</v>
+        <v>3.548206044000001</v>
       </c>
       <c r="P29">
-        <v>11.947472229</v>
+        <v>11.878776756</v>
       </c>
       <c r="Q29">
-        <v>22.147472229</v>
+        <v>22.078776756</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1010524625019843</v>
+        <v>0.1016824810440956</v>
       </c>
       <c r="T29">
-        <v>0.8547380225169241</v>
+        <v>0.8644842089934799</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.441457524347266</v>
+        <v>7.175691184192005</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08491846635174885</v>
+        <v>0.08477966507704918</v>
       </c>
       <c r="C30">
-        <v>126.0977084266558</v>
+        <v>125.0572838666974</v>
       </c>
       <c r="D30">
-        <v>169.2217084266558</v>
+        <v>169.8242838666974</v>
       </c>
       <c r="E30">
-        <v>-44.696</v>
+        <v>-43.05299999999999</v>
       </c>
       <c r="F30">
-        <v>46.004</v>
+        <v>47.64700000000001</v>
       </c>
       <c r="G30">
         <v>2.88</v>
@@ -3747,28 +3747,28 @@
         <v>17.925</v>
       </c>
       <c r="M30">
-        <v>2.4980172</v>
+        <v>2.587232100000001</v>
       </c>
       <c r="N30">
-        <v>15.4269828</v>
+        <v>15.3377679</v>
       </c>
       <c r="O30">
-        <v>3.548206044000001</v>
+        <v>3.527686617</v>
       </c>
       <c r="P30">
-        <v>11.878776756</v>
+        <v>11.810081283</v>
       </c>
       <c r="Q30">
-        <v>22.078776756</v>
+        <v>22.010081283</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1016824810440956</v>
+        <v>0.1023302465873932</v>
       </c>
       <c r="T30">
-        <v>0.8644842089934799</v>
+        <v>0.8745049359341639</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.175691184192005</v>
+        <v>6.9282535571509</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08477966507704916</v>
+        <v>0.08464086380234948</v>
       </c>
       <c r="C31">
-        <v>125.0572838666974</v>
+        <v>124.0211660203902</v>
       </c>
       <c r="D31">
-        <v>169.8242838666974</v>
+        <v>170.4311660203902</v>
       </c>
       <c r="E31">
-        <v>-43.053</v>
+        <v>-41.41</v>
       </c>
       <c r="F31">
-        <v>47.647</v>
+        <v>49.29</v>
       </c>
       <c r="G31">
         <v>2.88</v>
@@ -3829,28 +3829,28 @@
         <v>17.925</v>
       </c>
       <c r="M31">
-        <v>2.5872321</v>
+        <v>2.676447</v>
       </c>
       <c r="N31">
-        <v>15.3377679</v>
+        <v>15.248553</v>
       </c>
       <c r="O31">
-        <v>3.527686617000001</v>
+        <v>3.507167190000001</v>
       </c>
       <c r="P31">
-        <v>11.810081283</v>
+        <v>11.74138581</v>
       </c>
       <c r="Q31">
-        <v>22.010081283</v>
+        <v>21.94138581</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1023302465873932</v>
+        <v>0.1029965197176421</v>
       </c>
       <c r="T31">
-        <v>0.8745049359341639</v>
+        <v>0.8848119693588674</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.928253557150903</v>
+        <v>6.697311771912539</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08464086380234948</v>
+        <v>0.0845020625276498</v>
       </c>
       <c r="C32">
-        <v>124.0211660203902</v>
+        <v>122.9894012245937</v>
       </c>
       <c r="D32">
-        <v>170.4311660203902</v>
+        <v>171.0424012245937</v>
       </c>
       <c r="E32">
-        <v>-41.41</v>
+        <v>-39.767</v>
       </c>
       <c r="F32">
-        <v>49.29</v>
+        <v>50.933</v>
       </c>
       <c r="G32">
         <v>2.88</v>
@@ -3911,28 +3911,28 @@
         <v>17.925</v>
       </c>
       <c r="M32">
-        <v>2.676447</v>
+        <v>2.7656619</v>
       </c>
       <c r="N32">
-        <v>15.248553</v>
+        <v>15.1593381</v>
       </c>
       <c r="O32">
-        <v>3.507167190000001</v>
+        <v>3.486647763000001</v>
       </c>
       <c r="P32">
-        <v>11.74138581</v>
+        <v>11.672690337</v>
       </c>
       <c r="Q32">
-        <v>21.94138581</v>
+        <v>21.872690337</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1029965197176421</v>
+        <v>0.1036821051125359</v>
       </c>
       <c r="T32">
-        <v>0.8848119693588674</v>
+        <v>0.8954177573755913</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.697311771912539</v>
+        <v>6.481269456689555</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0845020625276498</v>
+        <v>0.08436326125295011</v>
       </c>
       <c r="C33">
-        <v>122.9894012245937</v>
+        <v>121.9620364832909</v>
       </c>
       <c r="D33">
-        <v>171.0424012245937</v>
+        <v>171.6580364832909</v>
       </c>
       <c r="E33">
-        <v>-39.767</v>
+        <v>-38.124</v>
       </c>
       <c r="F33">
-        <v>50.933</v>
+        <v>52.57600000000001</v>
       </c>
       <c r="G33">
         <v>2.88</v>
@@ -3993,28 +3993,28 @@
         <v>17.925</v>
       </c>
       <c r="M33">
-        <v>2.7656619</v>
+        <v>2.8548768</v>
       </c>
       <c r="N33">
-        <v>15.1593381</v>
+        <v>15.0701232</v>
       </c>
       <c r="O33">
-        <v>3.486647763000001</v>
+        <v>3.466128336000001</v>
       </c>
       <c r="P33">
-        <v>11.672690337</v>
+        <v>11.603994864</v>
       </c>
       <c r="Q33">
-        <v>21.872690337</v>
+        <v>21.803994864</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1036821051125359</v>
+        <v>0.1043878547837502</v>
       </c>
       <c r="T33">
-        <v>0.8954177573755913</v>
+        <v>0.9063354803339835</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.481269456689555</v>
+        <v>6.278729786168006</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08436326125295011</v>
+        <v>0.08447855997825043</v>
       </c>
       <c r="C34">
-        <v>121.9620364832909</v>
+        <v>119.8073330278053</v>
       </c>
       <c r="D34">
-        <v>171.6580364832909</v>
+        <v>171.1463330278053</v>
       </c>
       <c r="E34">
-        <v>-38.124</v>
+        <v>-36.48099999999999</v>
       </c>
       <c r="F34">
-        <v>52.57600000000001</v>
+        <v>54.21900000000001</v>
       </c>
       <c r="G34">
         <v>2.88</v>
@@ -4075,45 +4075,45 @@
         <v>17.925</v>
       </c>
       <c r="M34">
-        <v>2.8548768</v>
+        <v>2.998310700000001</v>
       </c>
       <c r="N34">
-        <v>15.0701232</v>
+        <v>14.9266893</v>
       </c>
       <c r="O34">
-        <v>3.466128336000001</v>
+        <v>3.433138539</v>
       </c>
       <c r="P34">
-        <v>11.603994864</v>
+        <v>11.493550761</v>
       </c>
       <c r="Q34">
-        <v>21.803994864</v>
+        <v>21.693550761</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1043878547837502</v>
+        <v>0.105114671609329</v>
       </c>
       <c r="T34">
-        <v>0.9063354803339835</v>
+        <v>0.9175791054702382</v>
       </c>
       <c r="U34">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V34">
         <v>0.23</v>
       </c>
       <c r="W34">
-        <v>0.041811</v>
+        <v>0.042581</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>6.278729786168006</v>
+        <v>5.978366418130048</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08447855997825043</v>
+        <v>0.08434745870355075</v>
       </c>
       <c r="C35">
-        <v>119.8073330278053</v>
+        <v>118.7464077786385</v>
       </c>
       <c r="D35">
-        <v>171.1463330278053</v>
+        <v>171.7284077786385</v>
       </c>
       <c r="E35">
-        <v>-36.48099999999999</v>
+        <v>-34.83799999999999</v>
       </c>
       <c r="F35">
-        <v>54.21900000000001</v>
+        <v>55.86200000000001</v>
       </c>
       <c r="G35">
         <v>2.88</v>
@@ -4157,28 +4157,28 @@
         <v>17.925</v>
       </c>
       <c r="M35">
-        <v>2.998310700000001</v>
+        <v>3.089168600000001</v>
       </c>
       <c r="N35">
-        <v>14.9266893</v>
+        <v>14.8358314</v>
       </c>
       <c r="O35">
-        <v>3.433138539</v>
+        <v>3.412241222</v>
       </c>
       <c r="P35">
-        <v>11.493550761</v>
+        <v>11.423590178</v>
       </c>
       <c r="Q35">
-        <v>21.693550761</v>
+        <v>21.623590178</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.105114671609329</v>
+        <v>0.1058635131871981</v>
       </c>
       <c r="T35">
-        <v>0.9175791054702382</v>
+        <v>0.9291634465197128</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.978366418130048</v>
+        <v>5.802532111714458</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08434745870355075</v>
+        <v>0.08421635742885106</v>
       </c>
       <c r="C36">
-        <v>118.7464077786385</v>
+        <v>117.6894553549508</v>
       </c>
       <c r="D36">
-        <v>171.7284077786385</v>
+        <v>172.3144553549508</v>
       </c>
       <c r="E36">
-        <v>-34.83799999999999</v>
+        <v>-33.19499999999999</v>
       </c>
       <c r="F36">
-        <v>55.86200000000001</v>
+        <v>57.50500000000001</v>
       </c>
       <c r="G36">
         <v>2.88</v>
@@ -4239,28 +4239,28 @@
         <v>17.925</v>
       </c>
       <c r="M36">
-        <v>3.089168600000001</v>
+        <v>3.180026500000001</v>
       </c>
       <c r="N36">
-        <v>14.8358314</v>
+        <v>14.7449735</v>
       </c>
       <c r="O36">
-        <v>3.412241222</v>
+        <v>3.391343905</v>
       </c>
       <c r="P36">
-        <v>11.423590178</v>
+        <v>11.353629595</v>
       </c>
       <c r="Q36">
-        <v>21.623590178</v>
+        <v>21.553629595</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1058635131871981</v>
+        <v>0.1066353960443863</v>
       </c>
       <c r="T36">
-        <v>0.9291634465197128</v>
+        <v>0.9411042288322481</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.802532111714458</v>
+        <v>5.636745479951188</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08421635742885106</v>
+        <v>0.08408525615415138</v>
       </c>
       <c r="C37">
-        <v>117.6894553549508</v>
+        <v>116.6365165695149</v>
       </c>
       <c r="D37">
-        <v>172.3144553549508</v>
+        <v>172.9045165695149</v>
       </c>
       <c r="E37">
-        <v>-33.19499999999999</v>
+        <v>-31.55199999999999</v>
       </c>
       <c r="F37">
-        <v>57.50500000000001</v>
+        <v>59.14800000000001</v>
       </c>
       <c r="G37">
         <v>2.88</v>
@@ -4321,28 +4321,28 @@
         <v>17.925</v>
       </c>
       <c r="M37">
-        <v>3.180026500000001</v>
+        <v>3.270884400000001</v>
       </c>
       <c r="N37">
-        <v>14.7449735</v>
+        <v>14.6541156</v>
       </c>
       <c r="O37">
-        <v>3.391343905</v>
+        <v>3.370446588000001</v>
       </c>
       <c r="P37">
-        <v>11.353629595</v>
+        <v>11.283669012</v>
       </c>
       <c r="Q37">
-        <v>21.553629595</v>
+        <v>21.483669012</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1066353960443863</v>
+        <v>0.1074314002408615</v>
       </c>
       <c r="T37">
-        <v>0.9411042288322481</v>
+        <v>0.9534181605920502</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.636745479951188</v>
+        <v>5.480169216619211</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08408525615415138</v>
+        <v>0.08395415487945171</v>
       </c>
       <c r="C38">
-        <v>116.6365165695149</v>
+        <v>115.5876327960494</v>
       </c>
       <c r="D38">
-        <v>172.9045165695149</v>
+        <v>173.4986327960494</v>
       </c>
       <c r="E38">
-        <v>-31.552</v>
+        <v>-29.909</v>
       </c>
       <c r="F38">
-        <v>59.148</v>
+        <v>60.791</v>
       </c>
       <c r="G38">
         <v>2.88</v>
@@ -4403,28 +4403,28 @@
         <v>17.925</v>
       </c>
       <c r="M38">
-        <v>3.2708844</v>
+        <v>3.3617423</v>
       </c>
       <c r="N38">
-        <v>14.6541156</v>
+        <v>14.5632577</v>
       </c>
       <c r="O38">
-        <v>3.370446588000001</v>
+        <v>3.349549271</v>
       </c>
       <c r="P38">
-        <v>11.283669012</v>
+        <v>11.213708429</v>
       </c>
       <c r="Q38">
-        <v>21.483669012</v>
+        <v>21.413708429</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1074314002408615</v>
+        <v>0.1082526744118281</v>
       </c>
       <c r="T38">
-        <v>0.9534181605920502</v>
+        <v>0.9661230108204174</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.480169216619212</v>
+        <v>5.332056535088962</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08395415487945171</v>
+        <v>0.08382305360475203</v>
       </c>
       <c r="C39">
-        <v>115.5876327960494</v>
+        <v>114.5428459788899</v>
       </c>
       <c r="D39">
-        <v>173.4986327960494</v>
+        <v>174.0968459788899</v>
       </c>
       <c r="E39">
-        <v>-29.909</v>
+        <v>-28.266</v>
       </c>
       <c r="F39">
-        <v>60.791</v>
+        <v>62.434</v>
       </c>
       <c r="G39">
         <v>2.88</v>
@@ -4485,28 +4485,28 @@
         <v>17.925</v>
       </c>
       <c r="M39">
-        <v>3.3617423</v>
+        <v>3.4526002</v>
       </c>
       <c r="N39">
-        <v>14.5632577</v>
+        <v>14.4723998</v>
       </c>
       <c r="O39">
-        <v>3.349549271</v>
+        <v>3.328651954</v>
       </c>
       <c r="P39">
-        <v>11.213708429</v>
+        <v>11.143747846</v>
       </c>
       <c r="Q39">
-        <v>21.413708429</v>
+        <v>21.343747846</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1082526744118281</v>
+        <v>0.1091004412979872</v>
       </c>
       <c r="T39">
-        <v>0.9661230108204174</v>
+        <v>0.979237694927119</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.332056535088962</v>
+        <v>5.191739257849779</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08382305360475203</v>
+        <v>0.08369195233005235</v>
       </c>
       <c r="C40">
-        <v>114.5428459788899</v>
+        <v>113.5021986428598</v>
       </c>
       <c r="D40">
-        <v>174.0968459788899</v>
+        <v>174.6991986428598</v>
       </c>
       <c r="E40">
-        <v>-28.266</v>
+        <v>-26.62299999999999</v>
       </c>
       <c r="F40">
-        <v>62.434</v>
+        <v>64.07700000000001</v>
       </c>
       <c r="G40">
         <v>2.88</v>
@@ -4567,28 +4567,28 @@
         <v>17.925</v>
       </c>
       <c r="M40">
-        <v>3.4526002</v>
+        <v>3.543458100000001</v>
       </c>
       <c r="N40">
-        <v>14.4723998</v>
+        <v>14.3815419</v>
       </c>
       <c r="O40">
-        <v>3.328651954</v>
+        <v>3.307754637</v>
       </c>
       <c r="P40">
-        <v>11.143747846</v>
+        <v>11.073787263</v>
       </c>
       <c r="Q40">
-        <v>21.343747846</v>
+        <v>21.273787263</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1091004412979872</v>
+        <v>0.1099760038197579</v>
       </c>
       <c r="T40">
-        <v>0.979237694927119</v>
+        <v>0.9927823686766634</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.191739257849779</v>
+        <v>5.058617738417733</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08369195233005235</v>
+        <v>0.08356085105535266</v>
       </c>
       <c r="C41">
-        <v>113.5021986428598</v>
+        <v>112.4657339033474</v>
       </c>
       <c r="D41">
-        <v>174.6991986428598</v>
+        <v>175.3057339033475</v>
       </c>
       <c r="E41">
-        <v>-26.62299999999999</v>
+        <v>-24.97999999999999</v>
       </c>
       <c r="F41">
-        <v>64.07700000000001</v>
+        <v>65.72000000000001</v>
       </c>
       <c r="G41">
         <v>2.88</v>
@@ -4649,28 +4649,28 @@
         <v>17.925</v>
       </c>
       <c r="M41">
-        <v>3.543458100000001</v>
+        <v>3.634316000000001</v>
       </c>
       <c r="N41">
-        <v>14.3815419</v>
+        <v>14.290684</v>
       </c>
       <c r="O41">
-        <v>3.307754637</v>
+        <v>3.28685732</v>
       </c>
       <c r="P41">
-        <v>11.073787263</v>
+        <v>11.00382668</v>
       </c>
       <c r="Q41">
-        <v>21.273787263</v>
+        <v>21.20382668</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1099760038197579</v>
+        <v>0.1108807517589211</v>
       </c>
       <c r="T41">
-        <v>0.9927823686766634</v>
+        <v>1.006778531551192</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.058617738417733</v>
+        <v>4.932152294957289</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08356085105535266</v>
+        <v>0.08342974978065298</v>
       </c>
       <c r="C42">
-        <v>112.4657339033474</v>
+        <v>111.4334954765936</v>
       </c>
       <c r="D42">
-        <v>175.3057339033475</v>
+        <v>175.9164954765936</v>
       </c>
       <c r="E42">
-        <v>-24.97999999999999</v>
+        <v>-23.33699999999999</v>
       </c>
       <c r="F42">
-        <v>65.72000000000001</v>
+        <v>67.36300000000001</v>
       </c>
       <c r="G42">
         <v>2.88</v>
@@ -4731,28 +4731,28 @@
         <v>17.925</v>
       </c>
       <c r="M42">
-        <v>3.634316000000001</v>
+        <v>3.725173900000001</v>
       </c>
       <c r="N42">
-        <v>14.290684</v>
+        <v>14.1998261</v>
       </c>
       <c r="O42">
-        <v>3.28685732</v>
+        <v>3.265960003</v>
       </c>
       <c r="P42">
-        <v>11.00382668</v>
+        <v>10.933866097</v>
       </c>
       <c r="Q42">
-        <v>21.20382668</v>
+        <v>21.133866097</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1108807517589211</v>
+        <v>0.1118161691197508</v>
       </c>
       <c r="T42">
-        <v>1.006778531551192</v>
+        <v>1.021249140624858</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.932152294957289</v>
+        <v>4.811855897519306</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08342974978065298</v>
+        <v>0.0832986485059533</v>
       </c>
       <c r="C43">
-        <v>111.4334954765936</v>
+        <v>110.4055276901951</v>
       </c>
       <c r="D43">
-        <v>175.9164954765936</v>
+        <v>176.5315276901952</v>
       </c>
       <c r="E43">
-        <v>-23.33699999999999</v>
+        <v>-21.69399999999999</v>
       </c>
       <c r="F43">
-        <v>67.36300000000001</v>
+        <v>69.00600000000001</v>
       </c>
       <c r="G43">
         <v>2.88</v>
@@ -4813,28 +4813,28 @@
         <v>17.925</v>
       </c>
       <c r="M43">
-        <v>3.725173900000001</v>
+        <v>3.816031800000001</v>
       </c>
       <c r="N43">
-        <v>14.1998261</v>
+        <v>14.1089682</v>
       </c>
       <c r="O43">
-        <v>3.265960003</v>
+        <v>3.245062686</v>
       </c>
       <c r="P43">
-        <v>10.933866097</v>
+        <v>10.863905514</v>
       </c>
       <c r="Q43">
-        <v>21.133866097</v>
+        <v>21.063905514</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1118161691197508</v>
+        <v>0.1127838422516436</v>
       </c>
       <c r="T43">
-        <v>1.021249140624858</v>
+        <v>1.036218736218305</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.811855897519306</v>
+        <v>4.697287899959323</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08329864850595331</v>
+        <v>0.08316754723125364</v>
       </c>
       <c r="C44">
-        <v>110.4055276901951</v>
+        <v>109.3818754938291</v>
       </c>
       <c r="D44">
-        <v>176.5315276901951</v>
+        <v>177.1508754938291</v>
       </c>
       <c r="E44">
-        <v>-21.694</v>
+        <v>-20.051</v>
       </c>
       <c r="F44">
-        <v>69.006</v>
+        <v>70.649</v>
       </c>
       <c r="G44">
         <v>2.88</v>
@@ -4895,28 +4895,28 @@
         <v>17.925</v>
       </c>
       <c r="M44">
-        <v>3.8160318</v>
+        <v>3.9068897</v>
       </c>
       <c r="N44">
-        <v>14.1089682</v>
+        <v>14.0181103</v>
       </c>
       <c r="O44">
-        <v>3.245062686</v>
+        <v>3.224165369</v>
       </c>
       <c r="P44">
-        <v>10.863905514</v>
+        <v>10.793944931</v>
       </c>
       <c r="Q44">
-        <v>21.063905514</v>
+        <v>20.993944931</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1127838422516436</v>
+        <v>0.1137854688267607</v>
       </c>
       <c r="T44">
-        <v>1.036218736218305</v>
+        <v>1.051713580779944</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.697287899959324</v>
+        <v>4.588048646471898</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08316754723125364</v>
+        <v>0.08388344595655395</v>
       </c>
       <c r="C45">
-        <v>109.3818754938291</v>
+        <v>104.4087649230433</v>
       </c>
       <c r="D45">
-        <v>177.1508754938291</v>
+        <v>173.8207649230434</v>
       </c>
       <c r="E45">
-        <v>-20.051</v>
+        <v>-18.408</v>
       </c>
       <c r="F45">
-        <v>70.649</v>
+        <v>72.292</v>
       </c>
       <c r="G45">
         <v>2.88</v>
@@ -4977,45 +4977,45 @@
         <v>17.925</v>
       </c>
       <c r="M45">
-        <v>3.9068897</v>
+        <v>4.178477600000001</v>
       </c>
       <c r="N45">
-        <v>14.0181103</v>
+        <v>13.7465224</v>
       </c>
       <c r="O45">
-        <v>3.224165369</v>
+        <v>3.161700152</v>
       </c>
       <c r="P45">
-        <v>10.793944931</v>
+        <v>10.584822248</v>
       </c>
       <c r="Q45">
-        <v>20.993944931</v>
+        <v>20.784822248</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1137854688267607</v>
+        <v>0.1148228677795606</v>
       </c>
       <c r="T45">
-        <v>1.051713580779944</v>
+        <v>1.067761812647355</v>
       </c>
       <c r="U45">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V45">
         <v>0.23</v>
       </c>
       <c r="W45">
-        <v>0.042581</v>
+        <v>0.044506</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.588048646471898</v>
+        <v>4.289839916815636</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08388344595655395</v>
+        <v>0.08377159468185427</v>
       </c>
       <c r="C46">
-        <v>104.4087649230433</v>
+        <v>103.2777811891183</v>
       </c>
       <c r="D46">
-        <v>173.8207649230434</v>
+        <v>174.3327811891183</v>
       </c>
       <c r="E46">
-        <v>-18.408</v>
+        <v>-16.765</v>
       </c>
       <c r="F46">
-        <v>72.292</v>
+        <v>73.935</v>
       </c>
       <c r="G46">
         <v>2.88</v>
@@ -5059,28 +5059,28 @@
         <v>17.925</v>
       </c>
       <c r="M46">
-        <v>4.178477600000001</v>
+        <v>4.273443</v>
       </c>
       <c r="N46">
-        <v>13.7465224</v>
+        <v>13.651557</v>
       </c>
       <c r="O46">
-        <v>3.161700152</v>
+        <v>3.13985811</v>
       </c>
       <c r="P46">
-        <v>10.584822248</v>
+        <v>10.51169889</v>
       </c>
       <c r="Q46">
-        <v>20.784822248</v>
+        <v>20.71169889</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1148228677795606</v>
+        <v>0.1158979903306441</v>
       </c>
       <c r="T46">
-        <v>1.067761812647355</v>
+        <v>1.084393616582672</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.289839916815636</v>
+        <v>4.194510140886401</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08377159468185427</v>
+        <v>0.08365974340715458</v>
       </c>
       <c r="C47">
-        <v>103.2777811891183</v>
+        <v>102.1498228149488</v>
       </c>
       <c r="D47">
-        <v>174.3327811891183</v>
+        <v>174.8478228149488</v>
       </c>
       <c r="E47">
-        <v>-16.765</v>
+        <v>-15.122</v>
       </c>
       <c r="F47">
-        <v>73.935</v>
+        <v>75.578</v>
       </c>
       <c r="G47">
         <v>2.88</v>
@@ -5141,28 +5141,28 @@
         <v>17.925</v>
       </c>
       <c r="M47">
-        <v>4.273443</v>
+        <v>4.368408400000001</v>
       </c>
       <c r="N47">
-        <v>13.651557</v>
+        <v>13.5565916</v>
       </c>
       <c r="O47">
-        <v>3.13985811</v>
+        <v>3.118016068</v>
       </c>
       <c r="P47">
-        <v>10.51169889</v>
+        <v>10.438575532</v>
       </c>
       <c r="Q47">
-        <v>20.71169889</v>
+        <v>20.638575532</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1158979903306441</v>
+        <v>0.1170129322354714</v>
       </c>
       <c r="T47">
-        <v>1.084393616582672</v>
+        <v>1.101641413256334</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.194510140886401</v>
+        <v>4.103325137823652</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08365974340715458</v>
+        <v>0.08354789213245491</v>
       </c>
       <c r="C48">
-        <v>102.1498228149488</v>
+        <v>101.0249166939842</v>
       </c>
       <c r="D48">
-        <v>174.8478228149488</v>
+        <v>175.3659166939842</v>
       </c>
       <c r="E48">
-        <v>-15.122</v>
+        <v>-13.479</v>
       </c>
       <c r="F48">
-        <v>75.578</v>
+        <v>77.221</v>
       </c>
       <c r="G48">
         <v>2.88</v>
@@ -5223,28 +5223,28 @@
         <v>17.925</v>
       </c>
       <c r="M48">
-        <v>4.368408400000001</v>
+        <v>4.4633738</v>
       </c>
       <c r="N48">
-        <v>13.5565916</v>
+        <v>13.4616262</v>
       </c>
       <c r="O48">
-        <v>3.118016068</v>
+        <v>3.096174026</v>
       </c>
       <c r="P48">
-        <v>10.438575532</v>
+        <v>10.365452174</v>
       </c>
       <c r="Q48">
-        <v>20.638575532</v>
+        <v>20.565452174</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1170129322354714</v>
+        <v>0.1181699474197262</v>
       </c>
       <c r="T48">
-        <v>1.101641413256334</v>
+        <v>1.119540070181833</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.103325137823652</v>
+        <v>4.016020347657191</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08354789213245491</v>
+        <v>0.08472964085775521</v>
       </c>
       <c r="C49">
-        <v>101.0249166939842</v>
+        <v>94.05850646085456</v>
       </c>
       <c r="D49">
-        <v>175.3659166939842</v>
+        <v>170.0425064608546</v>
       </c>
       <c r="E49">
-        <v>-13.479</v>
+        <v>-11.83599999999998</v>
       </c>
       <c r="F49">
-        <v>77.221</v>
+        <v>78.86400000000002</v>
       </c>
       <c r="G49">
         <v>2.88</v>
@@ -5305,45 +5305,45 @@
         <v>17.925</v>
       </c>
       <c r="M49">
-        <v>4.4633738</v>
+        <v>4.834363200000001</v>
       </c>
       <c r="N49">
-        <v>13.4616262</v>
+        <v>13.0906368</v>
       </c>
       <c r="O49">
-        <v>3.096174026</v>
+        <v>3.010846464</v>
       </c>
       <c r="P49">
-        <v>10.365452174</v>
+        <v>10.079790336</v>
       </c>
       <c r="Q49">
-        <v>20.565452174</v>
+        <v>20.279790336</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1181699474197262</v>
+        <v>0.1193714631879908</v>
       </c>
       <c r="T49">
-        <v>1.119540070181833</v>
+        <v>1.138127136989081</v>
       </c>
       <c r="U49">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V49">
         <v>0.23</v>
       </c>
       <c r="W49">
-        <v>0.044506</v>
+        <v>0.047201</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.016020347657191</v>
+        <v>3.707830640445053</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0847296408577552</v>
+        <v>0.08464473958305552</v>
       </c>
       <c r="C50">
-        <v>94.05850646085466</v>
+        <v>92.78716104540365</v>
       </c>
       <c r="D50">
-        <v>170.0425064608547</v>
+        <v>170.4141610454037</v>
       </c>
       <c r="E50">
-        <v>-11.836</v>
+        <v>-10.193</v>
       </c>
       <c r="F50">
-        <v>78.864</v>
+        <v>80.50700000000001</v>
       </c>
       <c r="G50">
         <v>2.88</v>
@@ -5387,28 +5387,28 @@
         <v>17.925</v>
       </c>
       <c r="M50">
-        <v>4.8343632</v>
+        <v>4.9350791</v>
       </c>
       <c r="N50">
-        <v>13.0906368</v>
+        <v>12.9899209</v>
       </c>
       <c r="O50">
-        <v>3.010846464</v>
+        <v>2.987681807</v>
       </c>
       <c r="P50">
-        <v>10.079790336</v>
+        <v>10.002239093</v>
       </c>
       <c r="Q50">
-        <v>20.279790336</v>
+        <v>20.202239093</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1193714631879908</v>
+        <v>0.1206200972216775</v>
       </c>
       <c r="T50">
-        <v>1.138127136989081</v>
+        <v>1.157443108377006</v>
       </c>
       <c r="U50">
         <v>0.0613</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.707830640445054</v>
+        <v>3.632160627374747</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08464473958305552</v>
+        <v>0.08455983830835584</v>
       </c>
       <c r="C51">
-        <v>92.78716104540365</v>
+        <v>91.517443807435</v>
       </c>
       <c r="D51">
-        <v>170.4141610454037</v>
+        <v>170.787443807435</v>
       </c>
       <c r="E51">
-        <v>-10.193</v>
+        <v>-8.549999999999997</v>
       </c>
       <c r="F51">
-        <v>80.50700000000001</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="G51">
         <v>2.88</v>
@@ -5469,28 +5469,28 @@
         <v>17.925</v>
       </c>
       <c r="M51">
-        <v>4.9350791</v>
+        <v>5.035795</v>
       </c>
       <c r="N51">
-        <v>12.9899209</v>
+        <v>12.889205</v>
       </c>
       <c r="O51">
-        <v>2.987681807</v>
+        <v>2.96451715</v>
       </c>
       <c r="P51">
-        <v>10.002239093</v>
+        <v>9.92468785</v>
       </c>
       <c r="Q51">
-        <v>20.202239093</v>
+        <v>20.12468785</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1206200972216775</v>
+        <v>0.1219186766167117</v>
       </c>
       <c r="T51">
-        <v>1.157443108377006</v>
+        <v>1.177531718620447</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.632160627374747</v>
+        <v>3.559517414827252</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08455983830835584</v>
+        <v>0.08557449703365616</v>
       </c>
       <c r="C52">
-        <v>91.517443807435</v>
+        <v>85.51760756927169</v>
       </c>
       <c r="D52">
-        <v>170.787443807435</v>
+        <v>166.4306075692717</v>
       </c>
       <c r="E52">
-        <v>-8.549999999999997</v>
+        <v>-6.906999999999996</v>
       </c>
       <c r="F52">
-        <v>82.15000000000001</v>
+        <v>83.79300000000001</v>
       </c>
       <c r="G52">
         <v>2.88</v>
@@ -5551,45 +5551,45 @@
         <v>17.925</v>
       </c>
       <c r="M52">
-        <v>5.035795</v>
+        <v>5.371131300000001</v>
       </c>
       <c r="N52">
-        <v>12.889205</v>
+        <v>12.5538687</v>
       </c>
       <c r="O52">
-        <v>2.96451715</v>
+        <v>2.887389801</v>
       </c>
       <c r="P52">
-        <v>9.92468785</v>
+        <v>9.666478898999999</v>
       </c>
       <c r="Q52">
-        <v>20.12468785</v>
+        <v>19.866478899</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1219186766167117</v>
+        <v>0.1232702592523595</v>
       </c>
       <c r="T52">
-        <v>1.177531718620447</v>
+        <v>1.198440272139132</v>
       </c>
       <c r="U52">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V52">
         <v>0.23</v>
       </c>
       <c r="W52">
-        <v>0.047201</v>
+        <v>0.04935700000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.559517414827252</v>
+        <v>3.3372857595196</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08557449703365616</v>
+        <v>0.08551115575895649</v>
       </c>
       <c r="C53">
-        <v>85.51760756927169</v>
+        <v>84.14007269188025</v>
       </c>
       <c r="D53">
-        <v>166.4306075692717</v>
+        <v>166.6960726918803</v>
       </c>
       <c r="E53">
-        <v>-6.906999999999996</v>
+        <v>-5.263999999999996</v>
       </c>
       <c r="F53">
-        <v>83.79300000000001</v>
+        <v>85.43600000000001</v>
       </c>
       <c r="G53">
         <v>2.88</v>
@@ -5633,28 +5633,28 @@
         <v>17.925</v>
       </c>
       <c r="M53">
-        <v>5.371131300000001</v>
+        <v>5.476447600000001</v>
       </c>
       <c r="N53">
-        <v>12.5538687</v>
+        <v>12.4485524</v>
       </c>
       <c r="O53">
-        <v>2.887389801</v>
+        <v>2.863167052</v>
       </c>
       <c r="P53">
-        <v>9.666478898999999</v>
+        <v>9.585385348000001</v>
       </c>
       <c r="Q53">
-        <v>19.866478899</v>
+        <v>19.785385348</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1232702592523595</v>
+        <v>0.1246781578311593</v>
       </c>
       <c r="T53">
-        <v>1.198440272139132</v>
+        <v>1.220220015387761</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.3372857595196</v>
+        <v>3.273107187221147</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08551115575895649</v>
+        <v>0.08544781448425681</v>
       </c>
       <c r="C54">
-        <v>84.14007269188025</v>
+        <v>82.76338602766137</v>
       </c>
       <c r="D54">
-        <v>166.6960726918803</v>
+        <v>166.9623860276614</v>
       </c>
       <c r="E54">
-        <v>-5.263999999999996</v>
+        <v>-3.620999999999995</v>
       </c>
       <c r="F54">
-        <v>85.43600000000001</v>
+        <v>87.07900000000001</v>
       </c>
       <c r="G54">
         <v>2.88</v>
@@ -5715,28 +5715,28 @@
         <v>17.925</v>
       </c>
       <c r="M54">
-        <v>5.476447600000001</v>
+        <v>5.581763900000001</v>
       </c>
       <c r="N54">
-        <v>12.4485524</v>
+        <v>12.3432361</v>
       </c>
       <c r="O54">
-        <v>2.863167052</v>
+        <v>2.838944303</v>
       </c>
       <c r="P54">
-        <v>9.585385348000001</v>
+        <v>9.504291796999999</v>
       </c>
       <c r="Q54">
-        <v>19.785385348</v>
+        <v>19.704291797</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1246781578311593</v>
+        <v>0.1261459669877804</v>
       </c>
       <c r="T54">
-        <v>1.220220015387761</v>
+        <v>1.242926556221439</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.273107187221147</v>
+        <v>3.211350447839615</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08544781448425681</v>
+        <v>0.08538447320955712</v>
       </c>
       <c r="C55">
-        <v>82.76338602766137</v>
+        <v>81.38755164843158</v>
       </c>
       <c r="D55">
-        <v>166.9623860276614</v>
+        <v>167.2295516484316</v>
       </c>
       <c r="E55">
-        <v>-3.620999999999995</v>
+        <v>-1.977999999999994</v>
       </c>
       <c r="F55">
-        <v>87.07900000000001</v>
+        <v>88.72200000000001</v>
       </c>
       <c r="G55">
         <v>2.88</v>
@@ -5797,28 +5797,28 @@
         <v>17.925</v>
       </c>
       <c r="M55">
-        <v>5.581763900000001</v>
+        <v>5.6870802</v>
       </c>
       <c r="N55">
-        <v>12.3432361</v>
+        <v>12.2379198</v>
       </c>
       <c r="O55">
-        <v>2.838944303</v>
+        <v>2.814721554</v>
       </c>
       <c r="P55">
-        <v>9.504291796999999</v>
+        <v>9.423198246</v>
       </c>
       <c r="Q55">
-        <v>19.704291797</v>
+        <v>19.623198246</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1261459669877804</v>
+        <v>0.1276775939338198</v>
       </c>
       <c r="T55">
-        <v>1.242926556221439</v>
+        <v>1.266620337960928</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.211350447839615</v>
+        <v>3.151880995101845</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08538447320955712</v>
+        <v>0.08532113193485744</v>
       </c>
       <c r="C56">
-        <v>81.38755164843158</v>
+        <v>80.01257365211123</v>
       </c>
       <c r="D56">
-        <v>167.2295516484316</v>
+        <v>167.4975736521112</v>
       </c>
       <c r="E56">
-        <v>-1.977999999999994</v>
+        <v>-0.3349999999999937</v>
       </c>
       <c r="F56">
-        <v>88.72200000000001</v>
+        <v>90.36500000000001</v>
       </c>
       <c r="G56">
         <v>2.88</v>
@@ -5879,28 +5879,28 @@
         <v>17.925</v>
       </c>
       <c r="M56">
-        <v>5.6870802</v>
+        <v>5.792396500000001</v>
       </c>
       <c r="N56">
-        <v>12.2379198</v>
+        <v>12.1326035</v>
       </c>
       <c r="O56">
-        <v>2.814721554</v>
+        <v>2.790498805</v>
       </c>
       <c r="P56">
-        <v>9.423198246</v>
+        <v>9.342104695</v>
       </c>
       <c r="Q56">
-        <v>19.623198246</v>
+        <v>19.542104695</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1276775939338198</v>
+        <v>0.1292772931885721</v>
       </c>
       <c r="T56">
-        <v>1.266620337960928</v>
+        <v>1.291367176666618</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.151880995101845</v>
+        <v>3.094574067918175</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08532113193485744</v>
+        <v>0.08525779066015775</v>
       </c>
       <c r="C57">
-        <v>80.01257365211123</v>
+        <v>78.6384561629342</v>
       </c>
       <c r="D57">
-        <v>167.4975736521112</v>
+        <v>167.7664561629342</v>
       </c>
       <c r="E57">
-        <v>-0.3349999999999937</v>
+        <v>1.308000000000007</v>
       </c>
       <c r="F57">
-        <v>90.36500000000001</v>
+        <v>92.00800000000001</v>
       </c>
       <c r="G57">
         <v>2.88</v>
@@ -5961,28 +5961,28 @@
         <v>17.925</v>
       </c>
       <c r="M57">
-        <v>5.792396500000001</v>
+        <v>5.897712800000001</v>
       </c>
       <c r="N57">
-        <v>12.1326035</v>
+        <v>12.0272872</v>
       </c>
       <c r="O57">
-        <v>2.790498805</v>
+        <v>2.766276056</v>
       </c>
       <c r="P57">
-        <v>9.342104695</v>
+        <v>9.261011143999999</v>
       </c>
       <c r="Q57">
-        <v>19.542104695</v>
+        <v>19.461011144</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1292772931885721</v>
+        <v>0.1309497060458131</v>
       </c>
       <c r="T57">
-        <v>1.291367176666618</v>
+        <v>1.317238871677111</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.094574067918175</v>
+        <v>3.03931381670535</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08525779066015775</v>
+        <v>0.08861786938545807</v>
       </c>
       <c r="C58">
-        <v>78.6384561629342</v>
+        <v>63.83019342887687</v>
       </c>
       <c r="D58">
-        <v>167.7664561629342</v>
+        <v>154.6011934288769</v>
       </c>
       <c r="E58">
-        <v>1.308000000000007</v>
+        <v>2.951000000000008</v>
       </c>
       <c r="F58">
-        <v>92.00800000000001</v>
+        <v>93.65100000000001</v>
       </c>
       <c r="G58">
         <v>2.88</v>
@@ -6043,45 +6043,45 @@
         <v>17.925</v>
       </c>
       <c r="M58">
-        <v>5.897712800000001</v>
+        <v>6.733506900000001</v>
       </c>
       <c r="N58">
-        <v>12.0272872</v>
+        <v>11.1914931</v>
       </c>
       <c r="O58">
-        <v>2.766276056</v>
+        <v>2.574043413</v>
       </c>
       <c r="P58">
-        <v>9.261011143999999</v>
+        <v>8.617449686999999</v>
       </c>
       <c r="Q58">
-        <v>19.461011144</v>
+        <v>18.817449687</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1309497060458131</v>
+        <v>0.1326999055475769</v>
       </c>
       <c r="T58">
-        <v>1.317238871677111</v>
+        <v>1.344313901339255</v>
       </c>
       <c r="U58">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V58">
         <v>0.23</v>
       </c>
       <c r="W58">
-        <v>0.04935700000000001</v>
+        <v>0.055363</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>3.03931381670535</v>
+        <v>2.662060092342075</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08861786938545807</v>
+        <v>0.08861458811075838</v>
       </c>
       <c r="C59">
-        <v>63.83019342887687</v>
+        <v>62.19904193675525</v>
       </c>
       <c r="D59">
-        <v>154.6011934288769</v>
+        <v>154.6130419367553</v>
       </c>
       <c r="E59">
-        <v>2.951000000000008</v>
+        <v>4.594000000000023</v>
       </c>
       <c r="F59">
-        <v>93.65100000000001</v>
+        <v>95.29400000000003</v>
       </c>
       <c r="G59">
         <v>2.88</v>
@@ -6125,28 +6125,28 @@
         <v>17.925</v>
       </c>
       <c r="M59">
-        <v>6.733506900000001</v>
+        <v>6.851638600000002</v>
       </c>
       <c r="N59">
-        <v>11.1914931</v>
+        <v>11.0733614</v>
       </c>
       <c r="O59">
-        <v>2.574043413</v>
+        <v>2.546873122</v>
       </c>
       <c r="P59">
-        <v>8.617449686999999</v>
+        <v>8.526488277999999</v>
       </c>
       <c r="Q59">
-        <v>18.817449687</v>
+        <v>18.726488278</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1326999055475769</v>
+        <v>0.1345334478827581</v>
       </c>
       <c r="T59">
-        <v>1.344313901339255</v>
+        <v>1.372678218128168</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.662060092342075</v>
+        <v>2.616162504543073</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0886145881107584</v>
+        <v>0.08861130683605872</v>
       </c>
       <c r="C60">
-        <v>62.19904193675522</v>
+        <v>60.56789226089246</v>
       </c>
       <c r="D60">
-        <v>154.6130419367552</v>
+        <v>154.6248922608925</v>
       </c>
       <c r="E60">
-        <v>4.593999999999994</v>
+        <v>6.236999999999995</v>
       </c>
       <c r="F60">
-        <v>95.294</v>
+        <v>96.937</v>
       </c>
       <c r="G60">
         <v>2.88</v>
@@ -6207,28 +6207,28 @@
         <v>17.925</v>
       </c>
       <c r="M60">
-        <v>6.8516386</v>
+        <v>6.9697703</v>
       </c>
       <c r="N60">
-        <v>11.0733614</v>
+        <v>10.9552297</v>
       </c>
       <c r="O60">
-        <v>2.546873122</v>
+        <v>2.519702831</v>
       </c>
       <c r="P60">
-        <v>8.526488277999999</v>
+        <v>8.435526869</v>
       </c>
       <c r="Q60">
-        <v>18.726488278</v>
+        <v>18.635526869</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1345334478827581</v>
+        <v>0.1364564313074603</v>
       </c>
       <c r="T60">
-        <v>1.372678218128168</v>
+        <v>1.402426160126296</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.616162504543074</v>
+        <v>2.571820767177937</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08861130683605872</v>
+        <v>0.08860802556135902</v>
       </c>
       <c r="C61">
-        <v>60.56789226089246</v>
+        <v>58.93674440170641</v>
       </c>
       <c r="D61">
-        <v>154.6248922608925</v>
+        <v>154.6367444017064</v>
       </c>
       <c r="E61">
-        <v>6.236999999999995</v>
+        <v>7.879999999999995</v>
       </c>
       <c r="F61">
-        <v>96.937</v>
+        <v>98.58</v>
       </c>
       <c r="G61">
         <v>2.88</v>
@@ -6289,28 +6289,28 @@
         <v>17.925</v>
       </c>
       <c r="M61">
-        <v>6.9697703</v>
+        <v>7.087902000000001</v>
       </c>
       <c r="N61">
-        <v>10.9552297</v>
+        <v>10.837098</v>
       </c>
       <c r="O61">
-        <v>2.519702831</v>
+        <v>2.49253254</v>
       </c>
       <c r="P61">
-        <v>8.435526869</v>
+        <v>8.34456546</v>
       </c>
       <c r="Q61">
-        <v>18.635526869</v>
+        <v>18.54456546</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1364564313074603</v>
+        <v>0.1384755639033975</v>
       </c>
       <c r="T61">
-        <v>1.402426160126296</v>
+        <v>1.43366149922433</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.571820767177937</v>
+        <v>2.528957087724971</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08860802556135902</v>
+        <v>0.09043657428665935</v>
       </c>
       <c r="C62">
-        <v>58.93674440170641</v>
+        <v>50.95901046705403</v>
       </c>
       <c r="D62">
-        <v>154.6367444017064</v>
+        <v>148.302010467054</v>
       </c>
       <c r="E62">
-        <v>7.879999999999995</v>
+        <v>9.522999999999996</v>
       </c>
       <c r="F62">
-        <v>98.58</v>
+        <v>100.223</v>
       </c>
       <c r="G62">
         <v>2.88</v>
@@ -6371,45 +6371,45 @@
         <v>17.925</v>
       </c>
       <c r="M62">
-        <v>7.087902000000001</v>
+        <v>7.5969034</v>
       </c>
       <c r="N62">
-        <v>10.837098</v>
+        <v>10.3280966</v>
       </c>
       <c r="O62">
-        <v>2.49253254</v>
+        <v>2.375462218</v>
       </c>
       <c r="P62">
-        <v>8.34456546</v>
+        <v>7.952634382</v>
       </c>
       <c r="Q62">
-        <v>18.54456546</v>
+        <v>18.152634382</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1384755639033975</v>
+        <v>0.140598241760665</v>
       </c>
       <c r="T62">
-        <v>1.43366149922433</v>
+        <v>1.466498650583802</v>
       </c>
       <c r="U62">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V62">
         <v>0.23</v>
       </c>
       <c r="W62">
-        <v>0.055363</v>
+        <v>0.05836600000000001</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.528957087724971</v>
+        <v>2.359514009352811</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09043657428665935</v>
+        <v>0.09046332301195967</v>
       </c>
       <c r="C63">
-        <v>50.95901046705403</v>
+        <v>49.22719285403393</v>
       </c>
       <c r="D63">
-        <v>148.302010467054</v>
+        <v>148.2131928540339</v>
       </c>
       <c r="E63">
-        <v>9.522999999999996</v>
+        <v>11.166</v>
       </c>
       <c r="F63">
-        <v>100.223</v>
+        <v>101.866</v>
       </c>
       <c r="G63">
         <v>2.88</v>
@@ -6453,28 +6453,28 @@
         <v>17.925</v>
       </c>
       <c r="M63">
-        <v>7.5969034</v>
+        <v>7.721442800000001</v>
       </c>
       <c r="N63">
-        <v>10.3280966</v>
+        <v>10.2035572</v>
       </c>
       <c r="O63">
-        <v>2.375462218</v>
+        <v>2.346818156</v>
       </c>
       <c r="P63">
-        <v>7.952634382</v>
+        <v>7.856739043999999</v>
       </c>
       <c r="Q63">
-        <v>18.152634382</v>
+        <v>18.056739044</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.140598241760665</v>
+        <v>0.142832639505157</v>
       </c>
       <c r="T63">
-        <v>1.466498650583802</v>
+        <v>1.501064073067457</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.359514009352811</v>
+        <v>2.321457331782604</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09046332301195967</v>
+        <v>0.09049007173725998</v>
       </c>
       <c r="C64">
-        <v>49.22719285403393</v>
+        <v>47.49548156252283</v>
       </c>
       <c r="D64">
-        <v>148.2131928540339</v>
+        <v>148.1244815625228</v>
       </c>
       <c r="E64">
-        <v>11.166</v>
+        <v>12.80900000000001</v>
       </c>
       <c r="F64">
-        <v>101.866</v>
+        <v>103.509</v>
       </c>
       <c r="G64">
         <v>2.88</v>
@@ -6535,28 +6535,28 @@
         <v>17.925</v>
       </c>
       <c r="M64">
-        <v>7.721442800000001</v>
+        <v>7.845982200000002</v>
       </c>
       <c r="N64">
-        <v>10.2035572</v>
+        <v>10.0790178</v>
       </c>
       <c r="O64">
-        <v>2.346818156</v>
+        <v>2.318174094</v>
       </c>
       <c r="P64">
-        <v>7.856739043999999</v>
+        <v>7.760843705999999</v>
       </c>
       <c r="Q64">
-        <v>18.056739044</v>
+        <v>17.960843706</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.142832639505157</v>
+        <v>0.1451878155061081</v>
       </c>
       <c r="T64">
-        <v>1.501064073067457</v>
+        <v>1.537497896766445</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.321457331782604</v>
+        <v>2.284608802706689</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09049007173725998</v>
+        <v>0.09051682046256029</v>
       </c>
       <c r="C65">
-        <v>47.49548156252283</v>
+        <v>45.76387640172246</v>
       </c>
       <c r="D65">
-        <v>148.1244815625228</v>
+        <v>148.0358764017225</v>
       </c>
       <c r="E65">
-        <v>12.80900000000001</v>
+        <v>14.45200000000001</v>
       </c>
       <c r="F65">
-        <v>103.509</v>
+        <v>105.152</v>
       </c>
       <c r="G65">
         <v>2.88</v>
@@ -6617,28 +6617,28 @@
         <v>17.925</v>
       </c>
       <c r="M65">
-        <v>7.845982200000002</v>
+        <v>7.970521600000001</v>
       </c>
       <c r="N65">
-        <v>10.0790178</v>
+        <v>9.954478399999999</v>
       </c>
       <c r="O65">
-        <v>2.318174094</v>
+        <v>2.289530032</v>
       </c>
       <c r="P65">
-        <v>7.760843705999999</v>
+        <v>7.664948367999999</v>
       </c>
       <c r="Q65">
-        <v>17.960843706</v>
+        <v>17.864948368</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1451878155061081</v>
+        <v>0.1476738346182231</v>
       </c>
       <c r="T65">
-        <v>1.537497896766445</v>
+        <v>1.575955821782043</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.284608802706689</v>
+        <v>2.248911790164398</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09051682046256029</v>
+        <v>0.09054356918786062</v>
       </c>
       <c r="C66">
-        <v>45.76387640172246</v>
+        <v>44.03237718129063</v>
       </c>
       <c r="D66">
-        <v>148.0358764017225</v>
+        <v>147.9473771812906</v>
       </c>
       <c r="E66">
-        <v>14.45200000000001</v>
+        <v>16.09500000000001</v>
       </c>
       <c r="F66">
-        <v>105.152</v>
+        <v>106.795</v>
       </c>
       <c r="G66">
         <v>2.88</v>
@@ -6699,28 +6699,28 @@
         <v>17.925</v>
       </c>
       <c r="M66">
-        <v>7.970521600000001</v>
+        <v>8.095061000000001</v>
       </c>
       <c r="N66">
-        <v>9.954478399999999</v>
+        <v>9.829939</v>
       </c>
       <c r="O66">
-        <v>2.289530032</v>
+        <v>2.26088597</v>
       </c>
       <c r="P66">
-        <v>7.664948367999999</v>
+        <v>7.569053029999999</v>
       </c>
       <c r="Q66">
-        <v>17.864948368</v>
+        <v>17.76905303</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1476738346182231</v>
+        <v>0.1503019119653161</v>
       </c>
       <c r="T66">
-        <v>1.575955821782043</v>
+        <v>1.616611342512818</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.248911790164398</v>
+        <v>2.214313147238792</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09054356918786062</v>
+        <v>0.09057031791316095</v>
       </c>
       <c r="C67">
-        <v>44.03237718129063</v>
+        <v>42.30098371134025</v>
       </c>
       <c r="D67">
-        <v>147.9473771812906</v>
+        <v>147.8589837113403</v>
       </c>
       <c r="E67">
-        <v>16.09500000000001</v>
+        <v>17.73800000000001</v>
       </c>
       <c r="F67">
-        <v>106.795</v>
+        <v>108.438</v>
       </c>
       <c r="G67">
         <v>2.88</v>
@@ -6781,28 +6781,28 @@
         <v>17.925</v>
       </c>
       <c r="M67">
-        <v>8.095061000000001</v>
+        <v>8.219600400000003</v>
       </c>
       <c r="N67">
-        <v>9.829939</v>
+        <v>9.705399599999998</v>
       </c>
       <c r="O67">
-        <v>2.26088597</v>
+        <v>2.232241908</v>
       </c>
       <c r="P67">
-        <v>7.569053029999999</v>
+        <v>7.473157691999998</v>
       </c>
       <c r="Q67">
-        <v>17.76905303</v>
+        <v>17.673157692</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1503019119653161</v>
+        <v>0.1530845820975322</v>
       </c>
       <c r="T67">
-        <v>1.616611342512818</v>
+        <v>1.65965836446305</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.214313147238792</v>
+        <v>2.180762948038203</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09057031791316095</v>
+        <v>0.09059706663846126</v>
       </c>
       <c r="C68">
-        <v>42.30098371134025</v>
+        <v>40.56969580243768</v>
       </c>
       <c r="D68">
-        <v>147.8589837113403</v>
+        <v>147.7706958024377</v>
       </c>
       <c r="E68">
-        <v>17.73800000000001</v>
+        <v>19.38100000000001</v>
       </c>
       <c r="F68">
-        <v>108.438</v>
+        <v>110.081</v>
       </c>
       <c r="G68">
         <v>2.88</v>
@@ -6863,28 +6863,28 @@
         <v>17.925</v>
       </c>
       <c r="M68">
-        <v>8.219600400000003</v>
+        <v>8.344139800000002</v>
       </c>
       <c r="N68">
-        <v>9.705399599999998</v>
+        <v>9.580860199999998</v>
       </c>
       <c r="O68">
-        <v>2.232241908</v>
+        <v>2.203597846</v>
       </c>
       <c r="P68">
-        <v>7.473157691999998</v>
+        <v>7.377262353999999</v>
       </c>
       <c r="Q68">
-        <v>17.673157692</v>
+        <v>17.577262354</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1530845820975322</v>
+        <v>0.156035898904428</v>
       </c>
       <c r="T68">
-        <v>1.65965836446305</v>
+        <v>1.705314296834509</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.180762948038203</v>
+        <v>2.148214247321215</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09059706663846126</v>
+        <v>0.09062381536376159</v>
       </c>
       <c r="C69">
-        <v>40.56969580243768</v>
+        <v>38.83851326560139</v>
       </c>
       <c r="D69">
-        <v>147.7706958024377</v>
+        <v>147.6825132656014</v>
       </c>
       <c r="E69">
-        <v>19.38100000000001</v>
+        <v>21.02400000000002</v>
       </c>
       <c r="F69">
-        <v>110.081</v>
+        <v>111.724</v>
       </c>
       <c r="G69">
         <v>2.88</v>
@@ -6945,28 +6945,28 @@
         <v>17.925</v>
       </c>
       <c r="M69">
-        <v>8.344139800000002</v>
+        <v>8.468679200000002</v>
       </c>
       <c r="N69">
-        <v>9.580860199999998</v>
+        <v>9.456320799999999</v>
       </c>
       <c r="O69">
-        <v>2.203597846</v>
+        <v>2.174953784</v>
       </c>
       <c r="P69">
-        <v>7.377262353999999</v>
+        <v>7.281367015999999</v>
       </c>
       <c r="Q69">
-        <v>17.577262354</v>
+        <v>17.481367016</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.156035898904428</v>
+        <v>0.1591716730117549</v>
       </c>
       <c r="T69">
-        <v>1.705314296834509</v>
+        <v>1.753823724979184</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.148214247321215</v>
+        <v>2.116622861331197</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09062381536376159</v>
+        <v>0.0906505640890619</v>
       </c>
       <c r="C70">
-        <v>38.83851326560139</v>
+        <v>37.10743591230084</v>
       </c>
       <c r="D70">
-        <v>147.6825132656014</v>
+        <v>147.5944359123009</v>
       </c>
       <c r="E70">
-        <v>21.02400000000002</v>
+        <v>22.66700000000002</v>
       </c>
       <c r="F70">
-        <v>111.724</v>
+        <v>113.367</v>
       </c>
       <c r="G70">
         <v>2.88</v>
@@ -7027,28 +7027,28 @@
         <v>17.925</v>
       </c>
       <c r="M70">
-        <v>8.468679200000002</v>
+        <v>8.593218600000002</v>
       </c>
       <c r="N70">
-        <v>9.456320799999999</v>
+        <v>9.331781399999999</v>
       </c>
       <c r="O70">
-        <v>2.174953784</v>
+        <v>2.146309722</v>
       </c>
       <c r="P70">
-        <v>7.281367015999999</v>
+        <v>7.185471677999999</v>
       </c>
       <c r="Q70">
-        <v>17.481367016</v>
+        <v>17.385471678</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1591716730117549</v>
+        <v>0.1625097551260061</v>
       </c>
       <c r="T70">
-        <v>1.753823724979184</v>
+        <v>1.805462793649322</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.116622861331197</v>
+        <v>2.085947167688716</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0906505640890619</v>
+        <v>0.0906773128143622</v>
       </c>
       <c r="C71">
-        <v>37.10743591230084</v>
+        <v>35.37646355445489</v>
       </c>
       <c r="D71">
-        <v>147.5944359123009</v>
+        <v>147.5064635544549</v>
       </c>
       <c r="E71">
-        <v>22.66700000000002</v>
+        <v>24.31000000000002</v>
       </c>
       <c r="F71">
-        <v>113.367</v>
+        <v>115.01</v>
       </c>
       <c r="G71">
         <v>2.88</v>
@@ -7109,28 +7109,28 @@
         <v>17.925</v>
       </c>
       <c r="M71">
-        <v>8.593218600000002</v>
+        <v>8.717758000000002</v>
       </c>
       <c r="N71">
-        <v>9.331781399999999</v>
+        <v>9.207241999999999</v>
       </c>
       <c r="O71">
-        <v>2.146309722</v>
+        <v>2.11766566</v>
       </c>
       <c r="P71">
-        <v>7.185471677999999</v>
+        <v>7.089576339999999</v>
       </c>
       <c r="Q71">
-        <v>17.385471678</v>
+        <v>17.28957634</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1625097551260061</v>
+        <v>0.166070376047874</v>
       </c>
       <c r="T71">
-        <v>1.805462793649322</v>
+        <v>1.860544466897468</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.085947167688716</v>
+        <v>2.05614792243602</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0906773128143622</v>
+        <v>0.09070406153966254</v>
       </c>
       <c r="C72">
-        <v>35.37646355445489</v>
+        <v>33.6455960044303</v>
       </c>
       <c r="D72">
-        <v>147.5064635544549</v>
+        <v>147.4185960044303</v>
       </c>
       <c r="E72">
-        <v>24.31000000000002</v>
+        <v>25.95300000000002</v>
       </c>
       <c r="F72">
-        <v>115.01</v>
+        <v>116.653</v>
       </c>
       <c r="G72">
         <v>2.88</v>
@@ -7191,28 +7191,28 @@
         <v>17.925</v>
       </c>
       <c r="M72">
-        <v>8.717758000000002</v>
+        <v>8.842297400000001</v>
       </c>
       <c r="N72">
-        <v>9.207241999999999</v>
+        <v>9.082702599999999</v>
       </c>
       <c r="O72">
-        <v>2.11766566</v>
+        <v>2.089021598</v>
       </c>
       <c r="P72">
-        <v>7.089576339999999</v>
+        <v>6.993681001999999</v>
       </c>
       <c r="Q72">
-        <v>17.28957634</v>
+        <v>17.193681002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.166070376047874</v>
+        <v>0.1698765570333191</v>
       </c>
       <c r="T72">
-        <v>1.860544466897468</v>
+        <v>1.919424876231695</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.05614792243602</v>
+        <v>2.027188092542556</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09070406153966254</v>
+        <v>0.09860329026496284</v>
       </c>
       <c r="C73">
-        <v>33.64559600443032</v>
+        <v>9.949174667269361</v>
       </c>
       <c r="D73">
-        <v>147.4185960044303</v>
+        <v>125.3651746672694</v>
       </c>
       <c r="E73">
-        <v>25.953</v>
+        <v>27.596</v>
       </c>
       <c r="F73">
-        <v>116.653</v>
+        <v>118.296</v>
       </c>
       <c r="G73">
         <v>2.88</v>
@@ -7273,45 +7273,45 @@
         <v>17.925</v>
       </c>
       <c r="M73">
-        <v>8.842297400000001</v>
+        <v>10.64664</v>
       </c>
       <c r="N73">
-        <v>9.082702599999999</v>
+        <v>7.278360000000001</v>
       </c>
       <c r="O73">
-        <v>2.089021598</v>
+        <v>1.6740228</v>
       </c>
       <c r="P73">
-        <v>6.993681001999999</v>
+        <v>5.604337200000001</v>
       </c>
       <c r="Q73">
-        <v>17.193681002</v>
+        <v>15.8043372</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1698765570333191</v>
+        <v>0.173954608089153</v>
       </c>
       <c r="T73">
-        <v>1.919424876231694</v>
+        <v>1.982511029089793</v>
       </c>
       <c r="U73">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V73">
         <v>0.23</v>
       </c>
       <c r="W73">
-        <v>0.05836600000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.027188092542556</v>
+        <v>1.683629764883569</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09860329026496284</v>
+        <v>0.09873937899026317</v>
       </c>
       <c r="C74">
-        <v>9.949174667269361</v>
+        <v>7.983904418865791</v>
       </c>
       <c r="D74">
-        <v>125.3651746672694</v>
+        <v>125.0429044188658</v>
       </c>
       <c r="E74">
-        <v>27.596</v>
+        <v>29.239</v>
       </c>
       <c r="F74">
-        <v>118.296</v>
+        <v>119.939</v>
       </c>
       <c r="G74">
         <v>2.88</v>
@@ -7355,28 +7355,28 @@
         <v>17.925</v>
       </c>
       <c r="M74">
-        <v>10.64664</v>
+        <v>10.79451</v>
       </c>
       <c r="N74">
-        <v>7.278360000000001</v>
+        <v>7.13049</v>
       </c>
       <c r="O74">
-        <v>1.6740228</v>
+        <v>1.6400127</v>
       </c>
       <c r="P74">
-        <v>5.604337200000001</v>
+        <v>5.4904773</v>
       </c>
       <c r="Q74">
-        <v>15.8043372</v>
+        <v>15.6904773</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.173954608089153</v>
+        <v>0.1783347370009747</v>
       </c>
       <c r="T74">
-        <v>1.982511029089793</v>
+        <v>2.050270230307751</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.683629764883569</v>
+        <v>1.660566343446808</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09873937899026317</v>
+        <v>0.09887546771556349</v>
       </c>
       <c r="C75">
-        <v>7.983904418865791</v>
+        <v>6.020286811473071</v>
       </c>
       <c r="D75">
-        <v>125.0429044188658</v>
+        <v>124.7222868114731</v>
       </c>
       <c r="E75">
-        <v>29.239</v>
+        <v>30.88200000000001</v>
       </c>
       <c r="F75">
-        <v>119.939</v>
+        <v>121.582</v>
       </c>
       <c r="G75">
         <v>2.88</v>
@@ -7437,28 +7437,28 @@
         <v>17.925</v>
       </c>
       <c r="M75">
-        <v>10.79451</v>
+        <v>10.94238</v>
       </c>
       <c r="N75">
-        <v>7.13049</v>
+        <v>6.982620000000001</v>
       </c>
       <c r="O75">
-        <v>1.6400127</v>
+        <v>1.6060026</v>
       </c>
       <c r="P75">
-        <v>5.4904773</v>
+        <v>5.376617400000001</v>
       </c>
       <c r="Q75">
-        <v>15.6904773</v>
+        <v>15.5766174</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1783347370009747</v>
+        <v>0.1830517989060134</v>
       </c>
       <c r="T75">
-        <v>2.050270230307751</v>
+        <v>2.123241677773245</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.660566343446808</v>
+        <v>1.638126257724553</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09887546771556349</v>
+        <v>0.09901155644086379</v>
       </c>
       <c r="C76">
-        <v>6.020286811473071</v>
+        <v>4.058309165187239</v>
       </c>
       <c r="D76">
-        <v>124.7222868114731</v>
+        <v>124.4033091651873</v>
       </c>
       <c r="E76">
-        <v>30.88200000000001</v>
+        <v>32.52500000000001</v>
       </c>
       <c r="F76">
-        <v>121.582</v>
+        <v>123.225</v>
       </c>
       <c r="G76">
         <v>2.88</v>
@@ -7519,28 +7519,28 @@
         <v>17.925</v>
       </c>
       <c r="M76">
-        <v>10.94238</v>
+        <v>11.09025</v>
       </c>
       <c r="N76">
-        <v>6.982620000000001</v>
+        <v>6.83475</v>
       </c>
       <c r="O76">
-        <v>1.6060026</v>
+        <v>1.5719925</v>
       </c>
       <c r="P76">
-        <v>5.376617400000001</v>
+        <v>5.262757499999999</v>
       </c>
       <c r="Q76">
-        <v>15.5766174</v>
+        <v>15.4627575</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1830517989060134</v>
+        <v>0.1881462257634552</v>
       </c>
       <c r="T76">
-        <v>2.123241677773245</v>
+        <v>2.202050841035978</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.638126257724553</v>
+        <v>1.616284574288226</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09901155644086379</v>
+        <v>0.09914764516616412</v>
       </c>
       <c r="C77">
-        <v>4.058309165187239</v>
+        <v>2.097958929488925</v>
       </c>
       <c r="D77">
-        <v>124.4033091651873</v>
+        <v>124.0859589294889</v>
       </c>
       <c r="E77">
-        <v>32.52500000000001</v>
+        <v>34.16800000000001</v>
       </c>
       <c r="F77">
-        <v>123.225</v>
+        <v>124.868</v>
       </c>
       <c r="G77">
         <v>2.88</v>
@@ -7601,28 +7601,28 @@
         <v>17.925</v>
       </c>
       <c r="M77">
-        <v>11.09025</v>
+        <v>11.23812</v>
       </c>
       <c r="N77">
-        <v>6.83475</v>
+        <v>6.68688</v>
       </c>
       <c r="O77">
-        <v>1.5719925</v>
+        <v>1.5379824</v>
       </c>
       <c r="P77">
-        <v>5.262757499999999</v>
+        <v>5.1488976</v>
       </c>
       <c r="Q77">
-        <v>15.4627575</v>
+        <v>15.3488976</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1881462257634552</v>
+        <v>0.1936651881923505</v>
       </c>
       <c r="T77">
-        <v>2.202050841035978</v>
+        <v>2.287427434570606</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.616284574288226</v>
+        <v>1.59501767199496</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09914764516616412</v>
+        <v>0.09928373389146443</v>
       </c>
       <c r="C78">
-        <v>2.097958929488925</v>
+        <v>0.1392236815974996</v>
       </c>
       <c r="D78">
-        <v>124.0859589294889</v>
+        <v>123.7702236815975</v>
       </c>
       <c r="E78">
-        <v>34.16800000000001</v>
+        <v>35.81100000000001</v>
       </c>
       <c r="F78">
-        <v>124.868</v>
+        <v>126.511</v>
       </c>
       <c r="G78">
         <v>2.88</v>
@@ -7683,28 +7683,28 @@
         <v>17.925</v>
       </c>
       <c r="M78">
-        <v>11.23812</v>
+        <v>11.38599</v>
       </c>
       <c r="N78">
-        <v>6.68688</v>
+        <v>6.539010000000001</v>
       </c>
       <c r="O78">
-        <v>1.5379824</v>
+        <v>1.5039723</v>
       </c>
       <c r="P78">
-        <v>5.1488976</v>
+        <v>5.035037700000001</v>
       </c>
       <c r="Q78">
-        <v>15.3488976</v>
+        <v>15.2350377</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1936651881923505</v>
+        <v>0.1996640603976715</v>
       </c>
       <c r="T78">
-        <v>2.287427434570606</v>
+        <v>2.38022807971694</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.59501767199496</v>
+        <v>1.574303156774246</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09928373389146443</v>
+        <v>0.09941982261676476</v>
       </c>
       <c r="C79">
-        <v>0.1392236815974996</v>
+        <v>-1.817908875150266</v>
       </c>
       <c r="D79">
-        <v>123.7702236815975</v>
+        <v>123.4560911248498</v>
       </c>
       <c r="E79">
-        <v>35.81100000000001</v>
+        <v>37.45400000000002</v>
       </c>
       <c r="F79">
-        <v>126.511</v>
+        <v>128.154</v>
       </c>
       <c r="G79">
         <v>2.88</v>
@@ -7765,28 +7765,28 @@
         <v>17.925</v>
       </c>
       <c r="M79">
-        <v>11.38599</v>
+        <v>11.53386</v>
       </c>
       <c r="N79">
-        <v>6.539010000000001</v>
+        <v>6.391139999999998</v>
       </c>
       <c r="O79">
-        <v>1.5039723</v>
+        <v>1.4699622</v>
       </c>
       <c r="P79">
-        <v>5.035037700000001</v>
+        <v>4.921177799999999</v>
       </c>
       <c r="Q79">
-        <v>15.2350377</v>
+        <v>15.1211778</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1996640603976715</v>
+        <v>0.206208284621658</v>
       </c>
       <c r="T79">
-        <v>2.38022807971694</v>
+        <v>2.481465147149305</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.574303156774246</v>
+        <v>1.554119782969448</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09941982261676476</v>
+        <v>0.09955591134206507</v>
       </c>
       <c r="C80">
-        <v>-1.817908875150266</v>
+        <v>-3.773450912896237</v>
       </c>
       <c r="D80">
-        <v>123.4560911248498</v>
+        <v>123.1435490871038</v>
       </c>
       <c r="E80">
-        <v>37.45400000000002</v>
+        <v>39.09700000000002</v>
       </c>
       <c r="F80">
-        <v>128.154</v>
+        <v>129.797</v>
       </c>
       <c r="G80">
         <v>2.88</v>
@@ -7847,28 +7847,28 @@
         <v>17.925</v>
       </c>
       <c r="M80">
-        <v>11.53386</v>
+        <v>11.68173</v>
       </c>
       <c r="N80">
-        <v>6.391139999999998</v>
+        <v>6.243269999999999</v>
       </c>
       <c r="O80">
-        <v>1.4699622</v>
+        <v>1.4359521</v>
       </c>
       <c r="P80">
-        <v>4.921177799999999</v>
+        <v>4.807317899999999</v>
       </c>
       <c r="Q80">
-        <v>15.1211778</v>
+        <v>15.0073179</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.206208284621658</v>
+        <v>0.213375768295548</v>
       </c>
       <c r="T80">
-        <v>2.481465147149305</v>
+        <v>2.592343840051419</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.554119782969448</v>
+        <v>1.534447380653379</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09955591134206507</v>
+        <v>0.09969200006736539</v>
       </c>
       <c r="C81">
-        <v>-3.773450912896237</v>
+        <v>-5.727414480833474</v>
       </c>
       <c r="D81">
-        <v>123.1435490871038</v>
+        <v>122.8325855191666</v>
       </c>
       <c r="E81">
-        <v>39.09700000000002</v>
+        <v>40.74000000000002</v>
       </c>
       <c r="F81">
-        <v>129.797</v>
+        <v>131.44</v>
       </c>
       <c r="G81">
         <v>2.88</v>
@@ -7929,28 +7929,28 @@
         <v>17.925</v>
       </c>
       <c r="M81">
-        <v>11.68173</v>
+        <v>11.8296</v>
       </c>
       <c r="N81">
-        <v>6.243269999999999</v>
+        <v>6.095399999999998</v>
       </c>
       <c r="O81">
-        <v>1.4359521</v>
+        <v>1.401942</v>
       </c>
       <c r="P81">
-        <v>4.807317899999999</v>
+        <v>4.693457999999998</v>
       </c>
       <c r="Q81">
-        <v>15.0073179</v>
+        <v>14.893458</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.213375768295548</v>
+        <v>0.221260000336827</v>
       </c>
       <c r="T81">
-        <v>2.592343840051419</v>
+        <v>2.714310402243744</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.534447380653379</v>
+        <v>1.515266788395212</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09969200006736539</v>
+        <v>0.1381711699896276</v>
       </c>
       <c r="C82">
-        <v>-5.727414480833474</v>
+        <v>-58.53893308586531</v>
       </c>
       <c r="D82">
-        <v>122.8325855191666</v>
+        <v>71.66406691413472</v>
       </c>
       <c r="E82">
-        <v>40.74000000000002</v>
+        <v>42.38300000000002</v>
       </c>
       <c r="F82">
-        <v>131.44</v>
+        <v>133.083</v>
       </c>
       <c r="G82">
         <v>2.88</v>
@@ -8011,45 +8011,45 @@
         <v>17.925</v>
       </c>
       <c r="M82">
-        <v>11.8296</v>
+        <v>19.53658440000001</v>
       </c>
       <c r="N82">
-        <v>6.095399999999998</v>
+        <v>-1.611584400000005</v>
       </c>
       <c r="O82">
-        <v>1.401942</v>
+        <v>-0.3706644120000012</v>
       </c>
       <c r="P82">
-        <v>4.693457999999998</v>
+        <v>-1.240919988000004</v>
       </c>
       <c r="Q82">
-        <v>14.893458</v>
+        <v>8.959080011999996</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.221260000336827</v>
+        <v>0.2334525684497493</v>
       </c>
       <c r="T82">
-        <v>2.714310402243744</v>
+        <v>2.902925553249327</v>
       </c>
       <c r="U82">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.23</v>
+        <v>0.211027163990856</v>
       </c>
       <c r="W82">
-        <v>0.0693</v>
+        <v>0.1158212123261424</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y82">
-        <v>1.515266788395212</v>
+        <v>0.9175094086558956</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1381711699896276</v>
+        <v>0.1391811699896277</v>
       </c>
       <c r="C83">
-        <v>-58.53893308586531</v>
+        <v>-60.95704339548466</v>
       </c>
       <c r="D83">
-        <v>71.66406691413472</v>
+        <v>70.88895660451537</v>
       </c>
       <c r="E83">
-        <v>42.38300000000002</v>
+        <v>44.02600000000002</v>
       </c>
       <c r="F83">
-        <v>133.083</v>
+        <v>134.726</v>
       </c>
       <c r="G83">
         <v>2.88</v>
@@ -8093,37 +8093,37 @@
         <v>17.925</v>
       </c>
       <c r="M83">
-        <v>19.53658440000001</v>
+        <v>19.77777680000001</v>
       </c>
       <c r="N83">
-        <v>-1.611584400000005</v>
+        <v>-1.852776800000004</v>
       </c>
       <c r="O83">
-        <v>-0.3706644120000012</v>
+        <v>-0.4261386640000011</v>
       </c>
       <c r="P83">
-        <v>-1.240919988000004</v>
+        <v>-1.426638136000003</v>
       </c>
       <c r="Q83">
-        <v>8.959080011999996</v>
+        <v>8.773361863999996</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2334525684497493</v>
+        <v>0.2438777111414021</v>
       </c>
       <c r="T83">
-        <v>2.902925553249327</v>
+        <v>3.064199195096513</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.211027163990856</v>
+        <v>0.2084536619909675</v>
       </c>
       <c r="W83">
-        <v>0.1158212123261424</v>
+        <v>0.116199002419726</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.9175094086558956</v>
+        <v>0.9063202695259457</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1391811699896277</v>
+        <v>0.1401911699896277</v>
       </c>
       <c r="C84">
-        <v>-60.95704339548466</v>
+        <v>-63.35856610664956</v>
       </c>
       <c r="D84">
-        <v>70.88895660451537</v>
+        <v>70.13043389335047</v>
       </c>
       <c r="E84">
-        <v>44.02600000000002</v>
+        <v>45.66900000000003</v>
       </c>
       <c r="F84">
-        <v>134.726</v>
+        <v>136.369</v>
       </c>
       <c r="G84">
         <v>2.88</v>
@@ -8175,37 +8175,37 @@
         <v>17.925</v>
       </c>
       <c r="M84">
-        <v>19.77777680000001</v>
+        <v>20.0189692</v>
       </c>
       <c r="N84">
-        <v>-1.852776800000004</v>
+        <v>-2.093969200000004</v>
       </c>
       <c r="O84">
-        <v>-0.4261386640000011</v>
+        <v>-0.4816129160000008</v>
       </c>
       <c r="P84">
-        <v>-1.426638136000003</v>
+        <v>-1.612356284000003</v>
       </c>
       <c r="Q84">
-        <v>8.773361863999996</v>
+        <v>8.587643715999997</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2438777111414021</v>
+        <v>0.2555293412085433</v>
       </c>
       <c r="T84">
-        <v>3.064199195096513</v>
+        <v>3.244446206572778</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2084536619909675</v>
+        <v>0.2059421720874619</v>
       </c>
       <c r="W84">
-        <v>0.116199002419726</v>
+        <v>0.1165676891375606</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.9063202695259457</v>
+        <v>0.8954007482063561</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1401911699896277</v>
+        <v>0.1412011699896277</v>
       </c>
       <c r="C85">
-        <v>-63.35856610664956</v>
+        <v>-65.74402805171782</v>
       </c>
       <c r="D85">
-        <v>70.13043389335047</v>
+        <v>69.38797194828221</v>
       </c>
       <c r="E85">
-        <v>45.66900000000003</v>
+        <v>47.31200000000003</v>
       </c>
       <c r="F85">
-        <v>136.369</v>
+        <v>138.012</v>
       </c>
       <c r="G85">
         <v>2.88</v>
@@ -8257,37 +8257,37 @@
         <v>17.925</v>
       </c>
       <c r="M85">
-        <v>20.0189692</v>
+        <v>20.26016160000001</v>
       </c>
       <c r="N85">
-        <v>-2.093969200000004</v>
+        <v>-2.335161600000006</v>
       </c>
       <c r="O85">
-        <v>-0.4816129160000008</v>
+        <v>-0.5370871680000014</v>
       </c>
       <c r="P85">
-        <v>-1.612356284000003</v>
+        <v>-1.798074432000005</v>
       </c>
       <c r="Q85">
-        <v>8.587643715999997</v>
+        <v>8.401925567999994</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2555293412085433</v>
+        <v>0.2686374250340773</v>
       </c>
       <c r="T85">
-        <v>3.244446206572778</v>
+        <v>3.447224094483577</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2059421720874619</v>
+        <v>0.2034904795626111</v>
       </c>
       <c r="W85">
-        <v>0.1165676891375606</v>
+        <v>0.1169275976002087</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8954007482063561</v>
+        <v>0.8847412154896136</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1412011699896276</v>
+        <v>0.1422111699896277</v>
       </c>
       <c r="C86">
-        <v>-65.74402805171776</v>
+        <v>-68.11393398673864</v>
       </c>
       <c r="D86">
-        <v>69.38797194828224</v>
+        <v>68.66106601326136</v>
       </c>
       <c r="E86">
-        <v>47.312</v>
+        <v>48.955</v>
       </c>
       <c r="F86">
-        <v>138.012</v>
+        <v>139.655</v>
       </c>
       <c r="G86">
         <v>2.88</v>
@@ -8339,37 +8339,37 @@
         <v>17.925</v>
       </c>
       <c r="M86">
-        <v>20.2601616</v>
+        <v>20.501354</v>
       </c>
       <c r="N86">
-        <v>-2.335161600000003</v>
+        <v>-2.576354000000002</v>
       </c>
       <c r="O86">
-        <v>-0.5370871680000007</v>
+        <v>-0.5925614200000004</v>
       </c>
       <c r="P86">
-        <v>-1.798074432000002</v>
+        <v>-1.983792580000002</v>
       </c>
       <c r="Q86">
-        <v>8.401925567999998</v>
+        <v>8.216207419999998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2686374250340772</v>
+        <v>0.2834932533696823</v>
       </c>
       <c r="T86">
-        <v>3.447224094483575</v>
+        <v>3.677039034115813</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2034904795626112</v>
+        <v>0.2010964739206981</v>
       </c>
       <c r="W86">
-        <v>0.1169275976002087</v>
+        <v>0.1172790376284415</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8847412154896137</v>
+        <v>0.874332495307383</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1422111699896277</v>
+        <v>0.1432211699896276</v>
       </c>
       <c r="C87">
-        <v>-68.11393398673864</v>
+        <v>-70.46876773581776</v>
       </c>
       <c r="D87">
-        <v>68.66106601326136</v>
+        <v>67.94923226418224</v>
       </c>
       <c r="E87">
-        <v>48.955</v>
+        <v>50.598</v>
       </c>
       <c r="F87">
-        <v>139.655</v>
+        <v>141.298</v>
       </c>
       <c r="G87">
         <v>2.88</v>
@@ -8421,37 +8421,37 @@
         <v>17.925</v>
       </c>
       <c r="M87">
-        <v>20.501354</v>
+        <v>20.7425464</v>
       </c>
       <c r="N87">
-        <v>-2.576354000000002</v>
+        <v>-2.817546400000001</v>
       </c>
       <c r="O87">
-        <v>-0.5925614200000004</v>
+        <v>-0.6480356720000003</v>
       </c>
       <c r="P87">
-        <v>-1.983792580000002</v>
+        <v>-2.169510728000001</v>
       </c>
       <c r="Q87">
-        <v>8.216207419999998</v>
+        <v>8.030489271999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2834932533696823</v>
+        <v>0.3004713428960882</v>
       </c>
       <c r="T87">
-        <v>3.677039034115813</v>
+        <v>3.9396846794098</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2010964739206981</v>
+        <v>0.198758142828597</v>
       </c>
       <c r="W87">
-        <v>0.1172790376284415</v>
+        <v>0.117622304632762</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.874332495307383</v>
+        <v>0.8641658383852042</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1432211699896276</v>
+        <v>0.1442311699896277</v>
       </c>
       <c r="C88">
-        <v>-70.46876773581776</v>
+        <v>-72.80899326502825</v>
       </c>
       <c r="D88">
-        <v>67.94923226418224</v>
+        <v>67.25200673497176</v>
       </c>
       <c r="E88">
-        <v>50.598</v>
+        <v>52.241</v>
       </c>
       <c r="F88">
-        <v>141.298</v>
+        <v>142.941</v>
       </c>
       <c r="G88">
         <v>2.88</v>
@@ -8503,37 +8503,37 @@
         <v>17.925</v>
       </c>
       <c r="M88">
-        <v>20.7425464</v>
+        <v>20.9837388</v>
       </c>
       <c r="N88">
-        <v>-2.817546400000001</v>
+        <v>-3.0587388</v>
       </c>
       <c r="O88">
-        <v>-0.6480356720000003</v>
+        <v>-0.7035099240000001</v>
       </c>
       <c r="P88">
-        <v>-2.169510728000001</v>
+        <v>-2.355228876</v>
       </c>
       <c r="Q88">
-        <v>8.030489271999999</v>
+        <v>7.844771123999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3004713428960882</v>
+        <v>0.3200614461957873</v>
       </c>
       <c r="T88">
-        <v>3.9396846794098</v>
+        <v>4.242737347056708</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.198758142828597</v>
+        <v>0.1964735664742453</v>
       </c>
       <c r="W88">
-        <v>0.117622304632762</v>
+        <v>0.1179576804415808</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8641658383852042</v>
+        <v>0.8542328977141099</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1442311699896277</v>
+        <v>0.1452411699896276</v>
       </c>
       <c r="C89">
-        <v>-72.80899326502825</v>
+        <v>-75.13505569087667</v>
       </c>
       <c r="D89">
-        <v>67.25200673497176</v>
+        <v>66.56894430912334</v>
       </c>
       <c r="E89">
-        <v>52.241</v>
+        <v>53.884</v>
       </c>
       <c r="F89">
-        <v>142.941</v>
+        <v>144.584</v>
       </c>
       <c r="G89">
         <v>2.88</v>
@@ -8585,37 +8585,37 @@
         <v>17.925</v>
       </c>
       <c r="M89">
-        <v>20.9837388</v>
+        <v>21.2249312</v>
       </c>
       <c r="N89">
-        <v>-3.0587388</v>
+        <v>-3.299931200000003</v>
       </c>
       <c r="O89">
-        <v>-0.7035099240000001</v>
+        <v>-0.7589841760000008</v>
       </c>
       <c r="P89">
-        <v>-2.355228876</v>
+        <v>-2.540947024000002</v>
       </c>
       <c r="Q89">
-        <v>7.844771123999999</v>
+        <v>7.659052975999996</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3200614461957873</v>
+        <v>0.342916566712103</v>
       </c>
       <c r="T89">
-        <v>4.242737347056708</v>
+        <v>4.596298792644768</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1964735664742453</v>
+        <v>0.1942409123097652</v>
       </c>
       <c r="W89">
-        <v>0.1179576804415808</v>
+        <v>0.1182854340729265</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8542328977141099</v>
+        <v>0.8445257056946313</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1452411699896276</v>
+        <v>0.1462511699896276</v>
       </c>
       <c r="C90">
-        <v>-75.13505569087667</v>
+        <v>-77.447382227931</v>
       </c>
       <c r="D90">
-        <v>66.56894430912334</v>
+        <v>65.89961777206901</v>
       </c>
       <c r="E90">
-        <v>53.884</v>
+        <v>55.527</v>
       </c>
       <c r="F90">
-        <v>144.584</v>
+        <v>146.227</v>
       </c>
       <c r="G90">
         <v>2.88</v>
@@ -8667,37 +8667,37 @@
         <v>17.925</v>
       </c>
       <c r="M90">
-        <v>21.2249312</v>
+        <v>21.4661236</v>
       </c>
       <c r="N90">
-        <v>-3.299931200000003</v>
+        <v>-3.541123600000002</v>
       </c>
       <c r="O90">
-        <v>-0.7589841760000008</v>
+        <v>-0.8144584280000006</v>
       </c>
       <c r="P90">
-        <v>-2.540947024000002</v>
+        <v>-2.726665172000002</v>
       </c>
       <c r="Q90">
-        <v>7.659052975999996</v>
+        <v>7.473334827999997</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.342916566712103</v>
+        <v>0.3699271636859305</v>
       </c>
       <c r="T90">
-        <v>4.596298792644768</v>
+        <v>5.014144137430655</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1942409123097652</v>
+        <v>0.1920584301489813</v>
       </c>
       <c r="W90">
-        <v>0.1182854340729265</v>
+        <v>0.1186058224541295</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8445257056946313</v>
+        <v>0.835036652821658</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1462511699896276</v>
+        <v>0.1472611699896277</v>
       </c>
       <c r="C91">
-        <v>-77.447382227931</v>
+        <v>-79.746383079849</v>
       </c>
       <c r="D91">
-        <v>65.89961777206901</v>
+        <v>65.24361692015101</v>
       </c>
       <c r="E91">
-        <v>55.527</v>
+        <v>57.17</v>
       </c>
       <c r="F91">
-        <v>146.227</v>
+        <v>147.87</v>
       </c>
       <c r="G91">
         <v>2.88</v>
@@ -8749,37 +8749,37 @@
         <v>17.925</v>
       </c>
       <c r="M91">
-        <v>21.4661236</v>
+        <v>21.707316</v>
       </c>
       <c r="N91">
-        <v>-3.541123600000002</v>
+        <v>-3.782316000000002</v>
       </c>
       <c r="O91">
-        <v>-0.8144584280000006</v>
+        <v>-0.8699326800000003</v>
       </c>
       <c r="P91">
-        <v>-2.726665172000002</v>
+        <v>-2.912383320000001</v>
       </c>
       <c r="Q91">
-        <v>7.473334827999997</v>
+        <v>7.287616679999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3699271636859305</v>
+        <v>0.4023398800545236</v>
       </c>
       <c r="T91">
-        <v>5.014144137430655</v>
+        <v>5.515558551173721</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1920584301489813</v>
+        <v>0.1899244475917704</v>
       </c>
       <c r="W91">
-        <v>0.1186058224541295</v>
+        <v>0.1189190910935281</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.835036652821658</v>
+        <v>0.8257584677903063</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1472611699896277</v>
+        <v>0.1482711699896277</v>
       </c>
       <c r="C92">
-        <v>-79.746383079849</v>
+        <v>-82.03245227771238</v>
       </c>
       <c r="D92">
-        <v>65.24361692015101</v>
+        <v>64.60054772228763</v>
       </c>
       <c r="E92">
-        <v>57.17</v>
+        <v>58.813</v>
       </c>
       <c r="F92">
-        <v>147.87</v>
+        <v>149.513</v>
       </c>
       <c r="G92">
         <v>2.88</v>
@@ -8831,37 +8831,37 @@
         <v>17.925</v>
       </c>
       <c r="M92">
-        <v>21.707316</v>
+        <v>21.9485084</v>
       </c>
       <c r="N92">
-        <v>-3.782316000000002</v>
+        <v>-4.023508400000001</v>
       </c>
       <c r="O92">
-        <v>-0.8699326800000003</v>
+        <v>-0.9254069320000002</v>
       </c>
       <c r="P92">
-        <v>-2.912383320000001</v>
+        <v>-3.098101468</v>
       </c>
       <c r="Q92">
-        <v>7.287616679999998</v>
+        <v>7.101898531999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4023398800545236</v>
+        <v>0.4419554222828041</v>
       </c>
       <c r="T92">
-        <v>5.515558551173721</v>
+        <v>6.128398390193025</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1899244475917704</v>
+        <v>0.1878373657501026</v>
       </c>
       <c r="W92">
-        <v>0.1189190910935281</v>
+        <v>0.1192254747078849</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8257584677903063</v>
+        <v>0.8166841989134896</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1482711699896277</v>
+        <v>0.1492811699896277</v>
       </c>
       <c r="C93">
-        <v>-82.03245227771238</v>
+        <v>-84.30596846926736</v>
       </c>
       <c r="D93">
-        <v>64.60054772228763</v>
+        <v>63.97003153073265</v>
       </c>
       <c r="E93">
-        <v>58.813</v>
+        <v>60.456</v>
       </c>
       <c r="F93">
-        <v>149.513</v>
+        <v>151.156</v>
       </c>
       <c r="G93">
         <v>2.88</v>
@@ -8913,37 +8913,37 @@
         <v>17.925</v>
       </c>
       <c r="M93">
-        <v>21.9485084</v>
+        <v>22.1897008</v>
       </c>
       <c r="N93">
-        <v>-4.023508400000001</v>
+        <v>-4.264700800000004</v>
       </c>
       <c r="O93">
-        <v>-0.9254069320000002</v>
+        <v>-0.9808811840000009</v>
       </c>
       <c r="P93">
-        <v>-3.098101468</v>
+        <v>-3.283819616000002</v>
       </c>
       <c r="Q93">
-        <v>7.101898531999999</v>
+        <v>6.916180383999997</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4419554222828041</v>
+        <v>0.4914748500681548</v>
       </c>
       <c r="T93">
-        <v>6.128398390193025</v>
+        <v>6.894448188967156</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1878373657501026</v>
+        <v>0.1857956552528189</v>
       </c>
       <c r="W93">
-        <v>0.1192254747078849</v>
+        <v>0.1195251978088862</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8166841989134896</v>
+        <v>0.8078071967513865</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1492811699896277</v>
+        <v>0.2024880094221273</v>
       </c>
       <c r="C94">
-        <v>-84.30596846926736</v>
+        <v>-107.6713913189827</v>
       </c>
       <c r="D94">
-        <v>63.97003153073265</v>
+        <v>42.24760868101731</v>
       </c>
       <c r="E94">
-        <v>60.456</v>
+        <v>62.099</v>
       </c>
       <c r="F94">
-        <v>151.156</v>
+        <v>152.799</v>
       </c>
       <c r="G94">
         <v>2.88</v>
@@ -8995,45 +8995,45 @@
         <v>17.925</v>
       </c>
       <c r="M94">
-        <v>22.1897008</v>
+        <v>30.6820392</v>
       </c>
       <c r="N94">
-        <v>-4.264700800000004</v>
+        <v>-12.7570392</v>
       </c>
       <c r="O94">
-        <v>-0.9808811840000009</v>
+        <v>-2.934119016</v>
       </c>
       <c r="P94">
-        <v>-3.283819616000002</v>
+        <v>-9.822920184000001</v>
       </c>
       <c r="Q94">
-        <v>6.916180383999997</v>
+        <v>0.3770798159999984</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4914748500681548</v>
+        <v>0.5833832491136004</v>
       </c>
       <c r="T94">
-        <v>6.894448188967156</v>
+        <v>8.316241891826632</v>
       </c>
       <c r="U94">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1857956552528189</v>
+        <v>0.1343701431683198</v>
       </c>
       <c r="W94">
-        <v>0.1195251978088862</v>
+        <v>0.1738184752518014</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.8078071967513865</v>
+        <v>0.5842180137753035</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2024880094221273</v>
+        <v>0.2040380094221273</v>
       </c>
       <c r="C95">
-        <v>-107.6713913189827</v>
+        <v>-109.7282223175823</v>
       </c>
       <c r="D95">
-        <v>42.24760868101731</v>
+        <v>41.83377768241769</v>
       </c>
       <c r="E95">
-        <v>62.099</v>
+        <v>63.742</v>
       </c>
       <c r="F95">
-        <v>152.799</v>
+        <v>154.442</v>
       </c>
       <c r="G95">
         <v>2.88</v>
@@ -9077,37 +9077,37 @@
         <v>17.925</v>
       </c>
       <c r="M95">
-        <v>30.6820392</v>
+        <v>31.0119536</v>
       </c>
       <c r="N95">
-        <v>-12.7570392</v>
+        <v>-13.0869536</v>
       </c>
       <c r="O95">
-        <v>-2.934119016</v>
+        <v>-3.009999328000001</v>
       </c>
       <c r="P95">
-        <v>-9.822920184000001</v>
+        <v>-10.076954272</v>
       </c>
       <c r="Q95">
-        <v>0.3770798159999984</v>
+        <v>0.1230457279999992</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5833832491136004</v>
+        <v>0.6729804572992006</v>
       </c>
       <c r="T95">
-        <v>8.316241891826632</v>
+        <v>9.702282207131073</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1343701431683198</v>
+        <v>0.1329406735601462</v>
       </c>
       <c r="W95">
-        <v>0.1738184752518014</v>
+        <v>0.1741055127491226</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5842180137753035</v>
+        <v>0.5780029285223747</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2040380094221273</v>
+        <v>0.2055880094221273</v>
       </c>
       <c r="C96">
-        <v>-109.7282223175823</v>
+        <v>-111.7770247031446</v>
       </c>
       <c r="D96">
-        <v>41.83377768241769</v>
+        <v>41.42797529685541</v>
       </c>
       <c r="E96">
-        <v>63.742</v>
+        <v>65.38500000000001</v>
       </c>
       <c r="F96">
-        <v>154.442</v>
+        <v>156.085</v>
       </c>
       <c r="G96">
         <v>2.88</v>
@@ -9159,37 +9159,37 @@
         <v>17.925</v>
       </c>
       <c r="M96">
-        <v>31.0119536</v>
+        <v>31.341868</v>
       </c>
       <c r="N96">
-        <v>-13.0869536</v>
+        <v>-13.416868</v>
       </c>
       <c r="O96">
-        <v>-3.009999328000001</v>
+        <v>-3.08587964</v>
       </c>
       <c r="P96">
-        <v>-10.076954272</v>
+        <v>-10.33098836</v>
       </c>
       <c r="Q96">
-        <v>0.1230457279999992</v>
+        <v>-0.1309883600000017</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6729804572992006</v>
+        <v>0.798416548759041</v>
       </c>
       <c r="T96">
-        <v>9.702282207131073</v>
+        <v>11.64273864855729</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1329406735601462</v>
+        <v>0.1315412980489867</v>
       </c>
       <c r="W96">
-        <v>0.1741055127491226</v>
+        <v>0.1743865073517635</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5780029285223747</v>
+        <v>0.5719186871695076</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2055880094221273</v>
+        <v>0.2071380094221273</v>
       </c>
       <c r="C97">
-        <v>-111.7770247031446</v>
+        <v>-113.8180298721691</v>
       </c>
       <c r="D97">
-        <v>41.42797529685541</v>
+        <v>41.02997012783094</v>
       </c>
       <c r="E97">
-        <v>65.38500000000001</v>
+        <v>67.02800000000003</v>
       </c>
       <c r="F97">
-        <v>156.085</v>
+        <v>157.728</v>
       </c>
       <c r="G97">
         <v>2.88</v>
@@ -9241,37 +9241,37 @@
         <v>17.925</v>
       </c>
       <c r="M97">
-        <v>31.341868</v>
+        <v>31.67178240000001</v>
       </c>
       <c r="N97">
-        <v>-13.416868</v>
+        <v>-13.74678240000001</v>
       </c>
       <c r="O97">
-        <v>-3.08587964</v>
+        <v>-3.161759952000002</v>
       </c>
       <c r="P97">
-        <v>-10.33098836</v>
+        <v>-10.58502244800001</v>
       </c>
       <c r="Q97">
-        <v>-0.1309883600000017</v>
+        <v>-0.3850224480000062</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.798416548759041</v>
+        <v>0.9865706859488017</v>
       </c>
       <c r="T97">
-        <v>11.64273864855729</v>
+        <v>14.55342331069662</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1315412980489867</v>
+        <v>0.1301710761943098</v>
       </c>
       <c r="W97">
-        <v>0.1743865073517635</v>
+        <v>0.1746616479001826</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5719186871695076</v>
+        <v>0.5659612008448252</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2071380094221273</v>
+        <v>0.2086880094221273</v>
       </c>
       <c r="C98">
-        <v>-113.8180298721691</v>
+        <v>-115.8514604135193</v>
       </c>
       <c r="D98">
-        <v>41.02997012783094</v>
+        <v>40.63953958648073</v>
       </c>
       <c r="E98">
-        <v>67.02800000000001</v>
+        <v>68.67100000000001</v>
       </c>
       <c r="F98">
-        <v>157.728</v>
+        <v>159.371</v>
       </c>
       <c r="G98">
         <v>2.88</v>
@@ -9323,37 +9323,37 @@
         <v>17.925</v>
       </c>
       <c r="M98">
-        <v>31.6717824</v>
+        <v>32.0016968</v>
       </c>
       <c r="N98">
-        <v>-13.7467824</v>
+        <v>-14.0766968</v>
       </c>
       <c r="O98">
-        <v>-3.161759952</v>
+        <v>-3.237640264000001</v>
       </c>
       <c r="P98">
-        <v>-10.585022448</v>
+        <v>-10.839056536</v>
       </c>
       <c r="Q98">
-        <v>-0.3850224480000008</v>
+        <v>-0.6390565360000036</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9865706859487994</v>
+        <v>1.300160914598399</v>
       </c>
       <c r="T98">
-        <v>14.55342331069659</v>
+        <v>19.40456441426211</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1301710761943098</v>
+        <v>0.1288291063366365</v>
       </c>
       <c r="W98">
-        <v>0.1746616479001826</v>
+        <v>0.1749311154476034</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5659612008448252</v>
+        <v>0.5601265492897238</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2086880094221273</v>
+        <v>0.2102380094221273</v>
       </c>
       <c r="C99">
-        <v>-115.8514604135193</v>
+        <v>-117.8775305235286</v>
       </c>
       <c r="D99">
-        <v>40.63953958648073</v>
+        <v>40.25646947647143</v>
       </c>
       <c r="E99">
-        <v>68.67100000000001</v>
+        <v>70.31400000000001</v>
       </c>
       <c r="F99">
-        <v>159.371</v>
+        <v>161.014</v>
       </c>
       <c r="G99">
         <v>2.88</v>
@@ -9405,37 +9405,37 @@
         <v>17.925</v>
       </c>
       <c r="M99">
-        <v>32.0016968</v>
+        <v>32.3316112</v>
       </c>
       <c r="N99">
-        <v>-14.0766968</v>
+        <v>-14.4066112</v>
       </c>
       <c r="O99">
-        <v>-3.237640264000001</v>
+        <v>-3.313520576000001</v>
       </c>
       <c r="P99">
-        <v>-10.839056536</v>
+        <v>-11.093090624</v>
       </c>
       <c r="Q99">
-        <v>-0.6390565360000036</v>
+        <v>-0.8930906240000027</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.300160914598399</v>
+        <v>1.927341371897599</v>
       </c>
       <c r="T99">
-        <v>19.40456441426211</v>
+        <v>29.10684662139317</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1288291063366365</v>
+        <v>0.1275145236189157</v>
       </c>
       <c r="W99">
-        <v>0.1749311154476034</v>
+        <v>0.1751950836573217</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5601265492897238</v>
+        <v>0.5544109722561552</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2102380094221273</v>
+        <v>0.2117880094221273</v>
       </c>
       <c r="C100">
-        <v>-117.8775305235286</v>
+        <v>-119.8964463978484</v>
       </c>
       <c r="D100">
-        <v>40.25646947647143</v>
+        <v>39.88055360215157</v>
       </c>
       <c r="E100">
-        <v>70.31400000000001</v>
+        <v>71.95700000000001</v>
       </c>
       <c r="F100">
-        <v>161.014</v>
+        <v>162.657</v>
       </c>
       <c r="G100">
         <v>2.88</v>
@@ -9487,37 +9487,37 @@
         <v>17.925</v>
       </c>
       <c r="M100">
-        <v>32.3316112</v>
+        <v>32.6615256</v>
       </c>
       <c r="N100">
-        <v>-14.4066112</v>
+        <v>-14.7365256</v>
       </c>
       <c r="O100">
-        <v>-3.313520576000001</v>
+        <v>-3.389400888000001</v>
       </c>
       <c r="P100">
-        <v>-11.093090624</v>
+        <v>-11.347124712</v>
       </c>
       <c r="Q100">
-        <v>-0.8930906240000027</v>
+        <v>-1.147124712000004</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.927341371897599</v>
+        <v>3.808882743795197</v>
       </c>
       <c r="T100">
-        <v>29.10684662139317</v>
+        <v>58.21369324278633</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1275145236189157</v>
+        <v>0.1262264981278156</v>
       </c>
       <c r="W100">
-        <v>0.1751950836573217</v>
+        <v>0.1754537191759346</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5544109722561552</v>
+        <v>0.548810861425285</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2117880094221273</v>
-      </c>
-      <c r="C101">
-        <v>-119.8964463978484</v>
-      </c>
-      <c r="D101">
-        <v>39.88055360215157</v>
-      </c>
-      <c r="E101">
-        <v>71.95700000000001</v>
-      </c>
-      <c r="F101">
-        <v>162.657</v>
-      </c>
-      <c r="G101">
-        <v>2.88</v>
-      </c>
-      <c r="H101">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>28.125</v>
-      </c>
-      <c r="K101">
-        <v>10.2</v>
-      </c>
-      <c r="L101">
-        <v>17.925</v>
-      </c>
-      <c r="M101">
-        <v>32.6615256</v>
-      </c>
-      <c r="N101">
-        <v>-14.7365256</v>
-      </c>
-      <c r="O101">
-        <v>-3.389400888000001</v>
-      </c>
-      <c r="P101">
-        <v>-11.347124712</v>
-      </c>
-      <c r="Q101">
-        <v>-1.147124712000004</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.808882743795197</v>
-      </c>
-      <c r="T101">
-        <v>58.21369324278633</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1262264981278156</v>
-      </c>
-      <c r="W101">
-        <v>0.1754537191759346</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.548810861425285</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
